--- a/research/traditional_assets/database/data/sweden/sweden_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_electronics_consumer_office.xlsx
@@ -1522,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1659,22 +1659,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09351268426607859</v>
+        <v>0.09335577813649047</v>
       </c>
       <c r="C2">
-        <v>180.4131566912018</v>
+        <v>178.9274899602388</v>
       </c>
       <c r="D2">
-        <v>176.8631566912018</v>
+        <v>177.2184899602388</v>
       </c>
       <c r="E2">
-        <v>-25.1</v>
+        <v>-23.259</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.841</v>
       </c>
       <c r="G2">
         <v>3.55</v>
@@ -1695,28 +1695,28 @@
         <v>11.59</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0926023</v>
       </c>
       <c r="N2">
-        <v>11.59</v>
+        <v>11.4973977</v>
       </c>
       <c r="O2">
-        <v>2.38754</v>
+        <v>2.3684639262</v>
       </c>
       <c r="P2">
-        <v>9.20246</v>
+        <v>9.1289337738</v>
       </c>
       <c r="Q2">
-        <v>15.31246</v>
+        <v>15.2389337738</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09351268426607859</v>
+        <v>0.09389534963281866</v>
       </c>
       <c r="T2">
-        <v>1.101909567345926</v>
+        <v>1.110747104684034</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>125.1588783431945</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1741,22 +1741,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09335577813649047</v>
+        <v>0.09319887200690234</v>
       </c>
       <c r="C3">
-        <v>178.9274899602388</v>
+        <v>177.4432538937034</v>
       </c>
       <c r="D3">
-        <v>177.2184899602388</v>
+        <v>177.5752538937034</v>
       </c>
       <c r="E3">
-        <v>-23.259</v>
+        <v>-21.418</v>
       </c>
       <c r="F3">
-        <v>1.841</v>
+        <v>3.682</v>
       </c>
       <c r="G3">
         <v>3.55</v>
@@ -1777,28 +1777,28 @@
         <v>11.59</v>
       </c>
       <c r="M3">
-        <v>0.0926023</v>
+        <v>0.1852046</v>
       </c>
       <c r="N3">
-        <v>11.4973977</v>
+        <v>11.4047954</v>
       </c>
       <c r="O3">
-        <v>2.3684639262</v>
+        <v>2.3493878524</v>
       </c>
       <c r="P3">
-        <v>9.1289337738</v>
+        <v>9.0554075476</v>
       </c>
       <c r="Q3">
-        <v>15.2389337738</v>
+        <v>15.1654075476</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09389534963281866</v>
+        <v>0.09428582449683913</v>
       </c>
       <c r="T3">
-        <v>1.110747104684034</v>
+        <v>1.119764999927001</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>125.1588783431945</v>
+        <v>62.57943917159724</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09319887200690234</v>
+        <v>0.09304196587731421</v>
       </c>
       <c r="C4">
-        <v>177.4432538937034</v>
+        <v>175.9604571493672</v>
       </c>
       <c r="D4">
-        <v>177.5752538937034</v>
+        <v>177.9334571493671</v>
       </c>
       <c r="E4">
-        <v>-21.418</v>
+        <v>-19.577</v>
       </c>
       <c r="F4">
-        <v>3.682</v>
+        <v>5.523</v>
       </c>
       <c r="G4">
         <v>3.55</v>
@@ -1859,28 +1859,28 @@
         <v>11.59</v>
       </c>
       <c r="M4">
-        <v>0.1852046</v>
+        <v>0.2778069</v>
       </c>
       <c r="N4">
-        <v>11.4047954</v>
+        <v>11.3121931</v>
       </c>
       <c r="O4">
-        <v>2.3493878524</v>
+        <v>2.3303117786</v>
       </c>
       <c r="P4">
-        <v>9.0554075476</v>
+        <v>8.9818813214</v>
       </c>
       <c r="Q4">
-        <v>15.1654075476</v>
+        <v>15.0918813214</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09428582449683913</v>
+        <v>0.09468435038898373</v>
       </c>
       <c r="T4">
-        <v>1.119764999927001</v>
+        <v>1.128968831154359</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.57943917159724</v>
+        <v>41.71962611439817</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1905,22 +1905,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09304196587731421</v>
+        <v>0.0928850597477261</v>
       </c>
       <c r="C5">
-        <v>175.9604571493672</v>
+        <v>174.4791084550001</v>
       </c>
       <c r="D5">
-        <v>177.9334571493671</v>
+        <v>178.2931084550001</v>
       </c>
       <c r="E5">
-        <v>-19.577</v>
+        <v>-17.736</v>
       </c>
       <c r="F5">
-        <v>5.523</v>
+        <v>7.364</v>
       </c>
       <c r="G5">
         <v>3.55</v>
@@ -1941,28 +1941,28 @@
         <v>11.59</v>
       </c>
       <c r="M5">
-        <v>0.2778069</v>
+        <v>0.3704092</v>
       </c>
       <c r="N5">
-        <v>11.3121931</v>
+        <v>11.2195908</v>
       </c>
       <c r="O5">
-        <v>2.3303117786</v>
+        <v>2.311235704800001</v>
       </c>
       <c r="P5">
-        <v>8.9818813214</v>
+        <v>8.908355095200001</v>
       </c>
       <c r="Q5">
-        <v>15.0918813214</v>
+        <v>15.0183550952</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09468435038898373</v>
+        <v>0.09509117890388136</v>
       </c>
       <c r="T5">
-        <v>1.128968831154359</v>
+        <v>1.13836440886562</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.71962611439817</v>
+        <v>31.28971958579863</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1987,22 +1987,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0928850597477261</v>
+        <v>0.09272815361813799</v>
       </c>
       <c r="C6">
-        <v>174.4791084550001</v>
+        <v>172.9992166090802</v>
       </c>
       <c r="D6">
-        <v>178.2931084550001</v>
+        <v>178.6542166090802</v>
       </c>
       <c r="E6">
-        <v>-17.736</v>
+        <v>-15.895</v>
       </c>
       <c r="F6">
-        <v>7.364</v>
+        <v>9.205</v>
       </c>
       <c r="G6">
         <v>3.55</v>
@@ -2023,28 +2023,28 @@
         <v>11.59</v>
       </c>
       <c r="M6">
-        <v>0.3704092</v>
+        <v>0.4630115</v>
       </c>
       <c r="N6">
-        <v>11.2195908</v>
+        <v>11.1269885</v>
       </c>
       <c r="O6">
-        <v>2.311235704800001</v>
+        <v>2.292159631</v>
       </c>
       <c r="P6">
-        <v>8.908355095200001</v>
+        <v>8.834828868999999</v>
       </c>
       <c r="Q6">
-        <v>15.0183550952</v>
+        <v>14.944828869</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09509117890388136</v>
+        <v>0.09550657222961893</v>
       </c>
       <c r="T6">
-        <v>1.13836440886562</v>
+        <v>1.147957788212908</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.28971958579863</v>
+        <v>25.0317756686389</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2069,22 +2069,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09272815361813799</v>
+        <v>0.09257124748854985</v>
       </c>
       <c r="C7">
-        <v>172.9992166090802</v>
+        <v>171.5207904815103</v>
       </c>
       <c r="D7">
-        <v>178.6542166090802</v>
+        <v>179.0167904815103</v>
       </c>
       <c r="E7">
-        <v>-15.895</v>
+        <v>-14.054</v>
       </c>
       <c r="F7">
-        <v>9.205</v>
+        <v>11.046</v>
       </c>
       <c r="G7">
         <v>3.55</v>
@@ -2105,28 +2105,28 @@
         <v>11.59</v>
       </c>
       <c r="M7">
-        <v>0.4630115</v>
+        <v>0.5556138</v>
       </c>
       <c r="N7">
-        <v>11.1269885</v>
+        <v>11.0343862</v>
       </c>
       <c r="O7">
-        <v>2.292159631</v>
+        <v>2.2730835572</v>
       </c>
       <c r="P7">
-        <v>8.834828868999999</v>
+        <v>8.7613026428</v>
       </c>
       <c r="Q7">
-        <v>14.944828869</v>
+        <v>14.8713026428</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09550657222961893</v>
+        <v>0.09593080371122326</v>
       </c>
       <c r="T7">
-        <v>1.147957788212908</v>
+        <v>1.157755282014394</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.0317756686389</v>
+        <v>20.85981305719908</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2151,22 +2151,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09257124748854985</v>
+        <v>0.09241434135896175</v>
       </c>
       <c r="C8">
-        <v>171.5207904815103</v>
+        <v>170.0438390143445</v>
       </c>
       <c r="D8">
-        <v>179.0167904815103</v>
+        <v>179.3808390143444</v>
       </c>
       <c r="E8">
-        <v>-14.054</v>
+        <v>-12.213</v>
       </c>
       <c r="F8">
-        <v>11.046</v>
+        <v>12.887</v>
       </c>
       <c r="G8">
         <v>3.55</v>
@@ -2187,28 +2187,28 @@
         <v>11.59</v>
       </c>
       <c r="M8">
-        <v>0.5556137999999999</v>
+        <v>0.6482160999999999</v>
       </c>
       <c r="N8">
-        <v>11.0343862</v>
+        <v>10.9417839</v>
       </c>
       <c r="O8">
-        <v>2.2730835572</v>
+        <v>2.2540074834</v>
       </c>
       <c r="P8">
-        <v>8.7613026428</v>
+        <v>8.6877764166</v>
       </c>
       <c r="Q8">
-        <v>14.8713026428</v>
+        <v>14.7977764166</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09593080371122326</v>
+        <v>0.09636415845049649</v>
       </c>
       <c r="T8">
-        <v>1.157755282014394</v>
+        <v>1.167763474607309</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.85981305719909</v>
+        <v>17.87983976331351</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2233,22 +2233,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09241434135896173</v>
+        <v>0.09225743522937363</v>
       </c>
       <c r="C9">
-        <v>170.0438390143445</v>
+        <v>168.5683712225235</v>
       </c>
       <c r="D9">
-        <v>179.3808390143445</v>
+        <v>179.7463712225235</v>
       </c>
       <c r="E9">
-        <v>-12.213</v>
+        <v>-10.372</v>
       </c>
       <c r="F9">
-        <v>12.887</v>
+        <v>14.728</v>
       </c>
       <c r="G9">
         <v>3.55</v>
@@ -2269,28 +2269,28 @@
         <v>11.59</v>
       </c>
       <c r="M9">
-        <v>0.6482161</v>
+        <v>0.7408184</v>
       </c>
       <c r="N9">
-        <v>10.9417839</v>
+        <v>10.8491816</v>
       </c>
       <c r="O9">
-        <v>2.2540074834</v>
+        <v>2.2349314096</v>
       </c>
       <c r="P9">
-        <v>8.6877764166</v>
+        <v>8.6142501904</v>
       </c>
       <c r="Q9">
-        <v>14.7977764166</v>
+        <v>14.7242501904</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09636415845049649</v>
+        <v>0.09680693394497134</v>
       </c>
       <c r="T9">
-        <v>1.167763474607309</v>
+        <v>1.177989236604418</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.8798397633135</v>
+        <v>15.64485979289931</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09225743522937363</v>
+        <v>0.0921005290997855</v>
       </c>
       <c r="C10">
-        <v>168.5683712225235</v>
+        <v>167.0943961946187</v>
       </c>
       <c r="D10">
-        <v>179.7463712225235</v>
+        <v>180.1133961946187</v>
       </c>
       <c r="E10">
-        <v>-10.372</v>
+        <v>-8.531000000000002</v>
       </c>
       <c r="F10">
-        <v>14.728</v>
+        <v>16.569</v>
       </c>
       <c r="G10">
         <v>3.55</v>
@@ -2351,28 +2351,28 @@
         <v>11.59</v>
       </c>
       <c r="M10">
-        <v>0.7408184</v>
+        <v>0.8334206999999999</v>
       </c>
       <c r="N10">
-        <v>10.8491816</v>
+        <v>10.7565793</v>
       </c>
       <c r="O10">
-        <v>2.2349314096</v>
+        <v>2.2158553358</v>
       </c>
       <c r="P10">
-        <v>8.6142501904</v>
+        <v>8.5407239642</v>
       </c>
       <c r="Q10">
-        <v>14.7242501904</v>
+        <v>14.6507239642</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09680693394497134</v>
+        <v>0.09725944076899505</v>
       </c>
       <c r="T10">
-        <v>1.177989236604418</v>
+        <v>1.188439740623442</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.64485979289931</v>
+        <v>13.90654203813272</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2397,22 +2397,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0921005290997855</v>
+        <v>0.09206272297019738</v>
       </c>
       <c r="C11">
-        <v>167.0943961946187</v>
+        <v>165.3420541127334</v>
       </c>
       <c r="D11">
-        <v>180.1133961946187</v>
+        <v>180.2020541127334</v>
       </c>
       <c r="E11">
-        <v>-8.531000000000002</v>
+        <v>-6.690000000000005</v>
       </c>
       <c r="F11">
-        <v>16.569</v>
+        <v>18.41</v>
       </c>
       <c r="G11">
         <v>3.55</v>
@@ -2433,45 +2433,45 @@
         <v>11.59</v>
       </c>
       <c r="M11">
-        <v>0.8334206999999999</v>
+        <v>0.9536379999999998</v>
       </c>
       <c r="N11">
-        <v>10.7565793</v>
+        <v>10.636362</v>
       </c>
       <c r="O11">
-        <v>2.2158553358</v>
+        <v>2.191090572</v>
       </c>
       <c r="P11">
-        <v>8.5407239642</v>
+        <v>8.445271428</v>
       </c>
       <c r="Q11">
-        <v>14.6507239642</v>
+        <v>14.555271428</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09725944076899505</v>
+        <v>0.09772200330021931</v>
       </c>
       <c r="T11">
-        <v>1.188439740623442</v>
+        <v>1.199122478065111</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.206</v>
       </c>
       <c r="W11">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.90654203813272</v>
+        <v>12.15345864992796</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2479,22 +2479,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09206272297019738</v>
+        <v>0.09191772684060925</v>
       </c>
       <c r="C12">
-        <v>165.3420541127334</v>
+        <v>163.8418906121029</v>
       </c>
       <c r="D12">
-        <v>180.2020541127334</v>
+        <v>180.5428906121029</v>
       </c>
       <c r="E12">
-        <v>-6.690000000000001</v>
+        <v>-4.849</v>
       </c>
       <c r="F12">
-        <v>18.41</v>
+        <v>20.251</v>
       </c>
       <c r="G12">
         <v>3.55</v>
@@ -2515,28 +2515,28 @@
         <v>11.59</v>
       </c>
       <c r="M12">
-        <v>0.953638</v>
+        <v>1.0490018</v>
       </c>
       <c r="N12">
-        <v>10.636362</v>
+        <v>10.5409982</v>
       </c>
       <c r="O12">
-        <v>2.191090572</v>
+        <v>2.1714456292</v>
       </c>
       <c r="P12">
-        <v>8.445271428</v>
+        <v>8.3695525708</v>
       </c>
       <c r="Q12">
-        <v>14.555271428</v>
+        <v>14.4795525708</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09772200330021931</v>
+        <v>0.09819496049506657</v>
       </c>
       <c r="T12">
-        <v>1.199122478065111</v>
+        <v>1.210045277022323</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.15345864992796</v>
+        <v>11.04859877266178</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09191772684060925</v>
+        <v>0.09177273071102113</v>
       </c>
       <c r="C13">
-        <v>163.8418906121029</v>
+        <v>162.3430188798796</v>
       </c>
       <c r="D13">
-        <v>180.5428906121029</v>
+        <v>180.8850188798796</v>
       </c>
       <c r="E13">
-        <v>-4.849</v>
+        <v>-3.008000000000003</v>
       </c>
       <c r="F13">
-        <v>20.251</v>
+        <v>22.092</v>
       </c>
       <c r="G13">
         <v>3.55</v>
@@ -2597,28 +2597,28 @@
         <v>11.59</v>
       </c>
       <c r="M13">
-        <v>1.0490018</v>
+        <v>1.1443656</v>
       </c>
       <c r="N13">
-        <v>10.5409982</v>
+        <v>10.4456344</v>
       </c>
       <c r="O13">
-        <v>2.1714456292</v>
+        <v>2.1518006864</v>
       </c>
       <c r="P13">
-        <v>8.3695525708</v>
+        <v>8.2938337136</v>
       </c>
       <c r="Q13">
-        <v>14.4795525708</v>
+        <v>14.4038337136</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09819496049506657</v>
+        <v>0.09867866671706947</v>
       </c>
       <c r="T13">
-        <v>1.210045277022323</v>
+        <v>1.22121632141038</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.04859877266178</v>
+        <v>10.1278822082733</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2643,22 +2643,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09177273071102113</v>
+        <v>0.09180320858143301</v>
       </c>
       <c r="C14">
-        <v>162.3430188798796</v>
+        <v>160.42999667388</v>
       </c>
       <c r="D14">
-        <v>180.8850188798796</v>
+        <v>180.81299667388</v>
       </c>
       <c r="E14">
-        <v>-3.008000000000003</v>
+        <v>-1.167000000000002</v>
       </c>
       <c r="F14">
-        <v>22.092</v>
+        <v>23.933</v>
       </c>
       <c r="G14">
         <v>3.55</v>
@@ -2679,45 +2679,45 @@
         <v>11.59</v>
       </c>
       <c r="M14">
-        <v>1.1443656</v>
+        <v>1.2804155</v>
       </c>
       <c r="N14">
-        <v>10.4456344</v>
+        <v>10.3095845</v>
       </c>
       <c r="O14">
-        <v>2.1518006864</v>
+        <v>2.123774407</v>
       </c>
       <c r="P14">
-        <v>8.2938337136</v>
+        <v>8.185810093000001</v>
       </c>
       <c r="Q14">
-        <v>14.4038337136</v>
+        <v>14.295810093</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09867866671706947</v>
+        <v>0.0991734926223368</v>
       </c>
       <c r="T14">
-        <v>1.22121632141038</v>
+        <v>1.232644171416554</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.206</v>
       </c>
       <c r="W14">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.1278822082733</v>
+        <v>9.051749217343902</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2725,22 +2725,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09180320858143301</v>
+        <v>0.09167171045184488</v>
       </c>
       <c r="C15">
-        <v>160.42999667388</v>
+        <v>158.9001504950855</v>
       </c>
       <c r="D15">
-        <v>180.81299667388</v>
+        <v>181.1241504950855</v>
       </c>
       <c r="E15">
-        <v>-1.167000000000002</v>
+        <v>0.6739999999999995</v>
       </c>
       <c r="F15">
-        <v>23.933</v>
+        <v>25.774</v>
       </c>
       <c r="G15">
         <v>3.55</v>
@@ -2761,28 +2761,28 @@
         <v>11.59</v>
       </c>
       <c r="M15">
-        <v>1.2804155</v>
+        <v>1.378909</v>
       </c>
       <c r="N15">
-        <v>10.3095845</v>
+        <v>10.211091</v>
       </c>
       <c r="O15">
-        <v>2.123774407</v>
+        <v>2.103484746</v>
       </c>
       <c r="P15">
-        <v>8.185810093000001</v>
+        <v>8.107606254</v>
       </c>
       <c r="Q15">
-        <v>14.295810093</v>
+        <v>14.217606254</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0991734926223368</v>
+        <v>0.09967982610679638</v>
       </c>
       <c r="T15">
-        <v>1.232644171416554</v>
+        <v>1.24433778537636</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.051749217343902</v>
+        <v>8.405195701819338</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2807,22 +2807,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09167171045184488</v>
+        <v>0.09154021232225676</v>
       </c>
       <c r="C16">
-        <v>158.9001504950855</v>
+        <v>157.3713770665623</v>
       </c>
       <c r="D16">
-        <v>181.1241504950855</v>
+        <v>181.4363770665623</v>
       </c>
       <c r="E16">
-        <v>0.6739999999999995</v>
+        <v>2.515000000000001</v>
       </c>
       <c r="F16">
-        <v>25.774</v>
+        <v>27.615</v>
       </c>
       <c r="G16">
         <v>3.55</v>
@@ -2843,28 +2843,28 @@
         <v>11.59</v>
       </c>
       <c r="M16">
-        <v>1.378909</v>
+        <v>1.4774025</v>
       </c>
       <c r="N16">
-        <v>10.211091</v>
+        <v>10.1125975</v>
       </c>
       <c r="O16">
-        <v>2.103484746</v>
+        <v>2.083195085</v>
       </c>
       <c r="P16">
-        <v>8.107606254</v>
+        <v>8.029402415</v>
       </c>
       <c r="Q16">
-        <v>14.217606254</v>
+        <v>14.139402415</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09967982610679638</v>
+        <v>0.1001980733203021</v>
       </c>
       <c r="T16">
-        <v>1.24433778537636</v>
+        <v>1.256306543194043</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.405195701819338</v>
+        <v>7.844849321698047</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2889,22 +2889,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09154021232225676</v>
+        <v>0.09151034619266864</v>
       </c>
       <c r="C17">
-        <v>157.3713770665623</v>
+        <v>155.6014406823964</v>
       </c>
       <c r="D17">
-        <v>181.4363770665623</v>
+        <v>181.5074406823964</v>
       </c>
       <c r="E17">
-        <v>2.514999999999997</v>
+        <v>4.355999999999998</v>
       </c>
       <c r="F17">
-        <v>27.615</v>
+        <v>29.456</v>
       </c>
       <c r="G17">
         <v>3.55</v>
@@ -2925,45 +2925,45 @@
         <v>11.59</v>
       </c>
       <c r="M17">
-        <v>1.4774025</v>
+        <v>1.5994608</v>
       </c>
       <c r="N17">
-        <v>10.1125975</v>
+        <v>9.990539200000001</v>
       </c>
       <c r="O17">
-        <v>2.083195085</v>
+        <v>2.0580510752</v>
       </c>
       <c r="P17">
-        <v>8.029402415</v>
+        <v>7.932488124800001</v>
       </c>
       <c r="Q17">
-        <v>14.139402415</v>
+        <v>14.0424881248</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1001980733203021</v>
+        <v>0.1007286597531769</v>
       </c>
       <c r="T17">
-        <v>1.256306543194043</v>
+        <v>1.268560271435957</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.206</v>
       </c>
       <c r="W17">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.844849321698048</v>
+        <v>7.246191966692776</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2971,22 +2971,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09151034619266864</v>
+        <v>0.09138520006308053</v>
       </c>
       <c r="C18">
-        <v>155.6014406823964</v>
+        <v>154.0588203296401</v>
       </c>
       <c r="D18">
-        <v>181.5074406823964</v>
+        <v>181.8058203296401</v>
       </c>
       <c r="E18">
-        <v>4.355999999999998</v>
+        <v>6.196999999999999</v>
       </c>
       <c r="F18">
-        <v>29.456</v>
+        <v>31.297</v>
       </c>
       <c r="G18">
         <v>3.55</v>
@@ -3007,28 +3007,28 @@
         <v>11.59</v>
       </c>
       <c r="M18">
-        <v>1.5994608</v>
+        <v>1.6994271</v>
       </c>
       <c r="N18">
-        <v>9.990539200000001</v>
+        <v>9.8905729</v>
       </c>
       <c r="O18">
-        <v>2.0580510752</v>
+        <v>2.0374580174</v>
       </c>
       <c r="P18">
-        <v>7.932488124800001</v>
+        <v>7.8531148826</v>
       </c>
       <c r="Q18">
-        <v>14.0424881248</v>
+        <v>13.9631148826</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1007286597531769</v>
+        <v>0.1012720314013018</v>
       </c>
       <c r="T18">
-        <v>1.268560271435957</v>
+        <v>1.281109270237917</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.246191966692776</v>
+        <v>6.81994538041673</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3053,22 +3053,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09138520006308053</v>
+        <v>0.0912600539334924</v>
       </c>
       <c r="C19">
-        <v>154.0588203296401</v>
+        <v>152.5171826033969</v>
       </c>
       <c r="D19">
-        <v>181.8058203296401</v>
+        <v>182.1051826033969</v>
       </c>
       <c r="E19">
-        <v>6.196999999999999</v>
+        <v>8.038000000000004</v>
       </c>
       <c r="F19">
-        <v>31.297</v>
+        <v>33.13800000000001</v>
       </c>
       <c r="G19">
         <v>3.55</v>
@@ -3089,28 +3089,28 @@
         <v>11.59</v>
       </c>
       <c r="M19">
-        <v>1.6994271</v>
+        <v>1.7993934</v>
       </c>
       <c r="N19">
-        <v>9.8905729</v>
+        <v>9.7906066</v>
       </c>
       <c r="O19">
-        <v>2.0374580174</v>
+        <v>2.0168649596</v>
       </c>
       <c r="P19">
-        <v>7.8531148826</v>
+        <v>7.7737416404</v>
       </c>
       <c r="Q19">
-        <v>13.9631148826</v>
+        <v>13.8837416404</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1012720314013018</v>
+        <v>0.1018286560164541</v>
       </c>
       <c r="T19">
-        <v>1.281109270237917</v>
+        <v>1.293964342181389</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.81994538041673</v>
+        <v>6.441059525949133</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3135,22 +3135,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0912600539334924</v>
+        <v>0.09128576780390429</v>
       </c>
       <c r="C20">
-        <v>152.5171826033969</v>
+        <v>150.6145919643068</v>
       </c>
       <c r="D20">
-        <v>182.1051826033969</v>
+        <v>182.0435919643068</v>
       </c>
       <c r="E20">
-        <v>8.037999999999997</v>
+        <v>9.878999999999998</v>
       </c>
       <c r="F20">
-        <v>33.138</v>
+        <v>34.979</v>
       </c>
       <c r="G20">
         <v>3.55</v>
@@ -3171,45 +3171,45 @@
         <v>11.59</v>
       </c>
       <c r="M20">
-        <v>1.7993934</v>
+        <v>1.9343387</v>
       </c>
       <c r="N20">
-        <v>9.7906066</v>
+        <v>9.6556613</v>
       </c>
       <c r="O20">
-        <v>2.0168649596</v>
+        <v>1.9890662278</v>
       </c>
       <c r="P20">
-        <v>7.7737416404</v>
+        <v>7.6665950722</v>
       </c>
       <c r="Q20">
-        <v>13.8837416404</v>
+        <v>13.7765950722</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1018286560164541</v>
+        <v>0.1023990244492645</v>
       </c>
       <c r="T20">
-        <v>1.293964342181389</v>
+        <v>1.30713682330865</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.441059525949134</v>
+        <v>5.991711792769281</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3217,22 +3217,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09128576780390429</v>
+        <v>0.09116856167431617</v>
       </c>
       <c r="C21">
-        <v>150.6145919643068</v>
+        <v>149.0546659844384</v>
       </c>
       <c r="D21">
-        <v>182.0435919643068</v>
+        <v>182.3246659844384</v>
       </c>
       <c r="E21">
-        <v>9.878999999999998</v>
+        <v>11.72</v>
       </c>
       <c r="F21">
-        <v>34.979</v>
+        <v>36.82</v>
       </c>
       <c r="G21">
         <v>3.55</v>
@@ -3253,28 +3253,28 @@
         <v>11.59</v>
       </c>
       <c r="M21">
-        <v>1.9343387</v>
+        <v>2.036146</v>
       </c>
       <c r="N21">
-        <v>9.6556613</v>
+        <v>9.553853999999999</v>
       </c>
       <c r="O21">
-        <v>1.9890662278</v>
+        <v>1.968093924</v>
       </c>
       <c r="P21">
-        <v>7.6665950722</v>
+        <v>7.585760076</v>
       </c>
       <c r="Q21">
-        <v>13.7765950722</v>
+        <v>13.695760076</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1023990244492645</v>
+        <v>0.1029836520928952</v>
       </c>
       <c r="T21">
-        <v>1.30713682330865</v>
+        <v>1.320638616464092</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.991711792769281</v>
+        <v>5.692126203130816</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3299,22 +3299,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09116856167431617</v>
+        <v>0.09105135554472804</v>
       </c>
       <c r="C22">
-        <v>149.0546659844384</v>
+        <v>147.4956092993585</v>
       </c>
       <c r="D22">
-        <v>182.3246659844384</v>
+        <v>182.6066092993585</v>
       </c>
       <c r="E22">
-        <v>11.72</v>
+        <v>13.561</v>
       </c>
       <c r="F22">
-        <v>36.82</v>
+        <v>38.661</v>
       </c>
       <c r="G22">
         <v>3.55</v>
@@ -3335,28 +3335,28 @@
         <v>11.59</v>
       </c>
       <c r="M22">
-        <v>2.036146</v>
+        <v>2.1379533</v>
       </c>
       <c r="N22">
-        <v>9.553853999999999</v>
+        <v>9.4520467</v>
       </c>
       <c r="O22">
-        <v>1.968093924</v>
+        <v>1.9471216202</v>
       </c>
       <c r="P22">
-        <v>7.585760076</v>
+        <v>7.5049250798</v>
       </c>
       <c r="Q22">
-        <v>13.695760076</v>
+        <v>13.6149250798</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1029836520928952</v>
+        <v>0.1035830804363646</v>
       </c>
       <c r="T22">
-        <v>1.320638616464092</v>
+        <v>1.334482227167773</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.692126203130816</v>
+        <v>5.421072574410302</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09105135554472804</v>
+        <v>0.09093414941513991</v>
       </c>
       <c r="C23">
-        <v>147.4956092993585</v>
+        <v>145.9374259480945</v>
       </c>
       <c r="D23">
-        <v>182.6066092993585</v>
+        <v>182.8894259480945</v>
       </c>
       <c r="E23">
-        <v>13.56099999999999</v>
+        <v>15.402</v>
       </c>
       <c r="F23">
-        <v>38.66099999999999</v>
+        <v>40.502</v>
       </c>
       <c r="G23">
         <v>3.55</v>
@@ -3417,28 +3417,28 @@
         <v>11.59</v>
       </c>
       <c r="M23">
-        <v>2.1379533</v>
+        <v>2.2397606</v>
       </c>
       <c r="N23">
-        <v>9.4520467</v>
+        <v>9.3502394</v>
       </c>
       <c r="O23">
-        <v>1.9471216202</v>
+        <v>1.9261493164</v>
       </c>
       <c r="P23">
-        <v>7.5049250798</v>
+        <v>7.424090083599999</v>
       </c>
       <c r="Q23">
-        <v>13.6149250798</v>
+        <v>13.5340900836</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1035830804363646</v>
+        <v>0.1041978787373589</v>
       </c>
       <c r="T23">
-        <v>1.334482227167773</v>
+        <v>1.348680802248472</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.421072574410302</v>
+        <v>5.174660184664378</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3463,22 +3463,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09093414941513991</v>
+        <v>0.09081694328555179</v>
       </c>
       <c r="C24">
-        <v>145.9374259480945</v>
+        <v>144.380119994735</v>
       </c>
       <c r="D24">
-        <v>182.8894259480945</v>
+        <v>183.173119994735</v>
       </c>
       <c r="E24">
-        <v>15.402</v>
+        <v>17.243</v>
       </c>
       <c r="F24">
-        <v>40.502</v>
+        <v>42.343</v>
       </c>
       <c r="G24">
         <v>3.55</v>
@@ -3499,28 +3499,28 @@
         <v>11.59</v>
       </c>
       <c r="M24">
-        <v>2.2397606</v>
+        <v>2.3415679</v>
       </c>
       <c r="N24">
-        <v>9.3502394</v>
+        <v>9.248432099999999</v>
       </c>
       <c r="O24">
-        <v>1.9261493164</v>
+        <v>1.9051770126</v>
       </c>
       <c r="P24">
-        <v>7.424090083599999</v>
+        <v>7.343255087399999</v>
       </c>
       <c r="Q24">
-        <v>13.5340900836</v>
+        <v>13.4532550874</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1041978787373589</v>
+        <v>0.1048286458253919</v>
       </c>
       <c r="T24">
-        <v>1.348680802248472</v>
+        <v>1.363248171487111</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.174660184664378</v>
+        <v>4.949674959244188</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3545,22 +3545,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09081694328555179</v>
+        <v>0.09069973715596369</v>
       </c>
       <c r="C25">
-        <v>144.380119994735</v>
+        <v>142.8236955286241</v>
       </c>
       <c r="D25">
-        <v>183.173119994735</v>
+        <v>183.4576955286241</v>
       </c>
       <c r="E25">
-        <v>17.243</v>
+        <v>19.084</v>
       </c>
       <c r="F25">
-        <v>42.343</v>
+        <v>44.184</v>
       </c>
       <c r="G25">
         <v>3.55</v>
@@ -3581,28 +3581,28 @@
         <v>11.59</v>
       </c>
       <c r="M25">
-        <v>2.3415679</v>
+        <v>2.4433752</v>
       </c>
       <c r="N25">
-        <v>9.248432099999999</v>
+        <v>9.1466248</v>
       </c>
       <c r="O25">
-        <v>1.9051770126</v>
+        <v>1.8842047088</v>
       </c>
       <c r="P25">
-        <v>7.343255087399999</v>
+        <v>7.262420091199999</v>
       </c>
       <c r="Q25">
-        <v>13.4532550874</v>
+        <v>13.3724200912</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1048286458253919</v>
+        <v>0.1054760120473206</v>
       </c>
       <c r="T25">
-        <v>1.363248171487111</v>
+        <v>1.37819889254782</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.949674959244188</v>
+        <v>4.743438502609013</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3627,22 +3627,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09069973715596368</v>
+        <v>0.09058253102637555</v>
       </c>
       <c r="C26">
-        <v>142.8236955286241</v>
+        <v>141.2681566645582</v>
       </c>
       <c r="D26">
-        <v>183.4576955286241</v>
+        <v>183.7431566645582</v>
       </c>
       <c r="E26">
-        <v>19.084</v>
+        <v>20.925</v>
       </c>
       <c r="F26">
-        <v>44.184</v>
+        <v>46.025</v>
       </c>
       <c r="G26">
         <v>3.55</v>
@@ -3663,28 +3663,28 @@
         <v>11.59</v>
       </c>
       <c r="M26">
-        <v>2.4433752</v>
+        <v>2.5451825</v>
       </c>
       <c r="N26">
-        <v>9.1466248</v>
+        <v>9.044817500000001</v>
       </c>
       <c r="O26">
-        <v>1.8842047088</v>
+        <v>1.863232405</v>
       </c>
       <c r="P26">
-        <v>7.262420091199999</v>
+        <v>7.181585095000001</v>
       </c>
       <c r="Q26">
-        <v>13.3724200912</v>
+        <v>13.291585095</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1054760120473206</v>
+        <v>0.1061406413685007</v>
       </c>
       <c r="T26">
-        <v>1.37819889254782</v>
+        <v>1.393548299503481</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.743438502609014</v>
+        <v>4.553700962504653</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3709,22 +3709,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09058253102637555</v>
+        <v>0.09098142489678743</v>
       </c>
       <c r="C27">
-        <v>141.2681566645582</v>
+        <v>138.4592455657955</v>
       </c>
       <c r="D27">
-        <v>183.7431566645582</v>
+        <v>182.7752455657955</v>
       </c>
       <c r="E27">
-        <v>20.925</v>
+        <v>22.766</v>
       </c>
       <c r="F27">
-        <v>46.025</v>
+        <v>47.866</v>
       </c>
       <c r="G27">
         <v>3.55</v>
@@ -3745,45 +3745,45 @@
         <v>11.59</v>
       </c>
       <c r="M27">
-        <v>2.5451825</v>
+        <v>2.7666548</v>
       </c>
       <c r="N27">
-        <v>9.044817500000001</v>
+        <v>8.8233452</v>
       </c>
       <c r="O27">
-        <v>1.863232405</v>
+        <v>1.8176091112</v>
       </c>
       <c r="P27">
-        <v>7.181585095000001</v>
+        <v>7.0057360888</v>
       </c>
       <c r="Q27">
-        <v>13.291585095</v>
+        <v>13.1157360888</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1061406413685007</v>
+        <v>0.1068232336443073</v>
       </c>
       <c r="T27">
-        <v>1.393548299503481</v>
+        <v>1.409312555295781</v>
       </c>
       <c r="U27">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V27">
         <v>0.206</v>
       </c>
       <c r="W27">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.553700962504653</v>
+        <v>4.189174594531996</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3791,22 +3791,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09098142489678743</v>
+        <v>0.09088406876719932</v>
       </c>
       <c r="C28">
-        <v>138.4592455657955</v>
+        <v>136.8535371151958</v>
       </c>
       <c r="D28">
-        <v>182.7752455657955</v>
+        <v>183.0105371151958</v>
       </c>
       <c r="E28">
-        <v>22.766</v>
+        <v>24.607</v>
       </c>
       <c r="F28">
-        <v>47.866</v>
+        <v>49.707</v>
       </c>
       <c r="G28">
         <v>3.55</v>
@@ -3827,28 +3827,28 @@
         <v>11.59</v>
       </c>
       <c r="M28">
-        <v>2.7666548</v>
+        <v>2.8730646</v>
       </c>
       <c r="N28">
-        <v>8.8233452</v>
+        <v>8.716935400000001</v>
       </c>
       <c r="O28">
-        <v>1.8176091112</v>
+        <v>1.7956886924</v>
       </c>
       <c r="P28">
-        <v>7.0057360888</v>
+        <v>6.9212467076</v>
       </c>
       <c r="Q28">
-        <v>13.1157360888</v>
+        <v>13.0312467076</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1068232336443073</v>
+        <v>0.1075245270783552</v>
       </c>
       <c r="T28">
-        <v>1.409312555295781</v>
+        <v>1.425508708507049</v>
       </c>
       <c r="U28">
         <v>0.0578</v>
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.189174594531996</v>
+        <v>4.0340199799197</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3873,22 +3873,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09088406876719932</v>
+        <v>0.09156483263761117</v>
       </c>
       <c r="C29">
-        <v>136.8535371151958</v>
+        <v>133.3798371966005</v>
       </c>
       <c r="D29">
-        <v>183.0105371151958</v>
+        <v>181.3778371966005</v>
       </c>
       <c r="E29">
-        <v>24.607</v>
+        <v>26.448</v>
       </c>
       <c r="F29">
-        <v>49.707</v>
+        <v>51.548</v>
       </c>
       <c r="G29">
         <v>3.55</v>
@@ -3909,45 +3909,45 @@
         <v>11.59</v>
       </c>
       <c r="M29">
-        <v>2.8730646</v>
+        <v>3.1598924</v>
       </c>
       <c r="N29">
-        <v>8.716935400000001</v>
+        <v>8.430107599999999</v>
       </c>
       <c r="O29">
-        <v>1.7956886924</v>
+        <v>1.7366021656</v>
       </c>
       <c r="P29">
-        <v>6.9212467076</v>
+        <v>6.6935054344</v>
       </c>
       <c r="Q29">
-        <v>13.0312467076</v>
+        <v>12.8035054344</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1075245270783552</v>
+        <v>0.1082453008855711</v>
       </c>
       <c r="T29">
-        <v>1.425508708507049</v>
+        <v>1.442154754863073</v>
       </c>
       <c r="U29">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V29">
         <v>0.206</v>
       </c>
       <c r="W29">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.0340199799197</v>
+        <v>3.667846411479074</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3955,22 +3955,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09156483263761117</v>
+        <v>0.09149526650802307</v>
       </c>
       <c r="C30">
-        <v>133.3798371966005</v>
+        <v>131.7043425116894</v>
       </c>
       <c r="D30">
-        <v>181.3778371966005</v>
+        <v>181.5433425116894</v>
       </c>
       <c r="E30">
-        <v>26.448</v>
+        <v>28.289</v>
       </c>
       <c r="F30">
-        <v>51.548</v>
+        <v>53.389</v>
       </c>
       <c r="G30">
         <v>3.55</v>
@@ -3991,28 +3991,28 @@
         <v>11.59</v>
       </c>
       <c r="M30">
-        <v>3.1598924</v>
+        <v>3.2727457</v>
       </c>
       <c r="N30">
-        <v>8.430107599999999</v>
+        <v>8.3172543</v>
       </c>
       <c r="O30">
-        <v>1.7366021656</v>
+        <v>1.7133543858</v>
       </c>
       <c r="P30">
-        <v>6.6935054344</v>
+        <v>6.603899914199999</v>
       </c>
       <c r="Q30">
-        <v>12.8035054344</v>
+        <v>12.7138999142</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1082453008855711</v>
+        <v>0.1089863781803142</v>
       </c>
       <c r="T30">
-        <v>1.442154754863073</v>
+        <v>1.459269703933352</v>
       </c>
       <c r="U30">
         <v>0.0613</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.667846411479074</v>
+        <v>3.541368949014279</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4037,22 +4037,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09149526650802306</v>
+        <v>0.09209266037843493</v>
       </c>
       <c r="C31">
-        <v>131.7043425116894</v>
+        <v>128.4518416859765</v>
       </c>
       <c r="D31">
-        <v>181.5433425116894</v>
+        <v>180.1318416859764</v>
       </c>
       <c r="E31">
-        <v>28.28899999999999</v>
+        <v>30.13</v>
       </c>
       <c r="F31">
-        <v>53.389</v>
+        <v>55.23</v>
       </c>
       <c r="G31">
         <v>3.55</v>
@@ -4073,45 +4073,45 @@
         <v>11.59</v>
       </c>
       <c r="M31">
-        <v>3.2727457</v>
+        <v>3.540243</v>
       </c>
       <c r="N31">
-        <v>8.3172543</v>
+        <v>8.049757</v>
       </c>
       <c r="O31">
-        <v>1.7133543858</v>
+        <v>1.658249942</v>
       </c>
       <c r="P31">
-        <v>6.603899914199999</v>
+        <v>6.391507057999999</v>
       </c>
       <c r="Q31">
-        <v>12.7138999142</v>
+        <v>12.501507058</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1089863781803142</v>
+        <v>0.1097486291120499</v>
       </c>
       <c r="T31">
-        <v>1.459269703933352</v>
+        <v>1.476873651548497</v>
       </c>
       <c r="U31">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V31">
         <v>0.206</v>
       </c>
       <c r="W31">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.541368949014279</v>
+        <v>3.273786573407532</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4119,22 +4119,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09209266037843493</v>
+        <v>0.09204532624884681</v>
       </c>
       <c r="C32">
-        <v>128.4518416859765</v>
+        <v>126.7218799236821</v>
       </c>
       <c r="D32">
-        <v>180.1318416859764</v>
+        <v>180.2428799236821</v>
       </c>
       <c r="E32">
-        <v>30.13</v>
+        <v>31.971</v>
       </c>
       <c r="F32">
-        <v>55.23</v>
+        <v>57.071</v>
       </c>
       <c r="G32">
         <v>3.55</v>
@@ -4155,28 +4155,28 @@
         <v>11.59</v>
       </c>
       <c r="M32">
-        <v>3.540243</v>
+        <v>3.6582511</v>
       </c>
       <c r="N32">
-        <v>8.049757</v>
+        <v>7.9317489</v>
       </c>
       <c r="O32">
-        <v>1.658249942</v>
+        <v>1.6339402734</v>
       </c>
       <c r="P32">
-        <v>6.391507057999999</v>
+        <v>6.297808626599999</v>
       </c>
       <c r="Q32">
-        <v>12.501507058</v>
+        <v>12.4078086266</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1097486291120499</v>
+        <v>0.110532974273691</v>
       </c>
       <c r="T32">
-        <v>1.476873651548497</v>
+        <v>1.494987858514804</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.273786573407532</v>
+        <v>3.168180554910514</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4201,22 +4201,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09204532624884681</v>
+        <v>0.09199799211925869</v>
       </c>
       <c r="C33">
-        <v>126.7218799236821</v>
+        <v>124.9920551398924</v>
       </c>
       <c r="D33">
-        <v>180.2428799236821</v>
+        <v>180.3540551398924</v>
       </c>
       <c r="E33">
-        <v>31.971</v>
+        <v>33.812</v>
       </c>
       <c r="F33">
-        <v>57.071</v>
+        <v>58.912</v>
       </c>
       <c r="G33">
         <v>3.55</v>
@@ -4237,28 +4237,28 @@
         <v>11.59</v>
       </c>
       <c r="M33">
-        <v>3.6582511</v>
+        <v>3.7762592</v>
       </c>
       <c r="N33">
-        <v>7.9317489</v>
+        <v>7.8137408</v>
       </c>
       <c r="O33">
-        <v>1.6339402734</v>
+        <v>1.6096306048</v>
       </c>
       <c r="P33">
-        <v>6.297808626599999</v>
+        <v>6.2041101952</v>
       </c>
       <c r="Q33">
-        <v>12.4078086266</v>
+        <v>12.3141101952</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.110532974273691</v>
+        <v>0.1113403884106746</v>
       </c>
       <c r="T33">
-        <v>1.494987858514804</v>
+        <v>1.513634836274239</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.168180554910514</v>
+        <v>3.069174912569561</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4283,22 +4283,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09199799211925869</v>
+        <v>0.09399441398967057</v>
       </c>
       <c r="C34">
-        <v>124.9920551398924</v>
+        <v>118.5780689551062</v>
       </c>
       <c r="D34">
-        <v>180.3540551398924</v>
+        <v>175.7810689551062</v>
       </c>
       <c r="E34">
-        <v>33.812</v>
+        <v>35.653</v>
       </c>
       <c r="F34">
-        <v>58.912</v>
+        <v>60.753</v>
       </c>
       <c r="G34">
         <v>3.55</v>
@@ -4319,45 +4319,45 @@
         <v>11.59</v>
       </c>
       <c r="M34">
-        <v>3.7762592</v>
+        <v>4.368140700000001</v>
       </c>
       <c r="N34">
-        <v>7.8137408</v>
+        <v>7.221859299999999</v>
       </c>
       <c r="O34">
-        <v>1.6096306048</v>
+        <v>1.4877030158</v>
       </c>
       <c r="P34">
-        <v>6.2041101952</v>
+        <v>5.734156284199999</v>
       </c>
       <c r="Q34">
-        <v>12.3141101952</v>
+        <v>11.8441562842</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1113403884106746</v>
+        <v>0.1121719044621949</v>
       </c>
       <c r="T34">
-        <v>1.513634836274239</v>
+        <v>1.532838440235448</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.206</v>
       </c>
       <c r="W34">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.069174912569561</v>
+        <v>2.653302811422718</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4365,22 +4365,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09399441398967057</v>
+        <v>0.09400901186008244</v>
       </c>
       <c r="C35">
-        <v>118.5780689551062</v>
+        <v>116.7044850784478</v>
       </c>
       <c r="D35">
-        <v>175.7810689551062</v>
+        <v>175.7484850784478</v>
       </c>
       <c r="E35">
-        <v>35.653</v>
+        <v>37.494</v>
       </c>
       <c r="F35">
-        <v>60.753</v>
+        <v>62.594</v>
       </c>
       <c r="G35">
         <v>3.55</v>
@@ -4401,28 +4401,28 @@
         <v>11.59</v>
       </c>
       <c r="M35">
-        <v>4.368140700000001</v>
+        <v>4.500508600000001</v>
       </c>
       <c r="N35">
-        <v>7.221859299999999</v>
+        <v>7.089491399999999</v>
       </c>
       <c r="O35">
-        <v>1.4877030158</v>
+        <v>1.4604352284</v>
       </c>
       <c r="P35">
-        <v>5.734156284199999</v>
+        <v>5.629056171599999</v>
       </c>
       <c r="Q35">
-        <v>11.8441562842</v>
+        <v>11.7390561716</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1121719044621949</v>
+        <v>0.1130286179698219</v>
       </c>
       <c r="T35">
-        <v>1.532838440235448</v>
+        <v>1.55262397158942</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.653302811422718</v>
+        <v>2.575264493439697</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09400901186008244</v>
+        <v>0.09402360973049434</v>
       </c>
       <c r="C36">
-        <v>116.7044850784478</v>
+        <v>114.8309132794522</v>
       </c>
       <c r="D36">
-        <v>175.7484850784478</v>
+        <v>175.7159132794522</v>
       </c>
       <c r="E36">
-        <v>37.494</v>
+        <v>39.335</v>
       </c>
       <c r="F36">
-        <v>62.594</v>
+        <v>64.435</v>
       </c>
       <c r="G36">
         <v>3.55</v>
@@ -4483,28 +4483,28 @@
         <v>11.59</v>
       </c>
       <c r="M36">
-        <v>4.500508600000001</v>
+        <v>4.632876500000001</v>
       </c>
       <c r="N36">
-        <v>7.089491399999999</v>
+        <v>6.957123499999999</v>
       </c>
       <c r="O36">
-        <v>1.4604352284</v>
+        <v>1.433167441</v>
       </c>
       <c r="P36">
-        <v>5.629056171599999</v>
+        <v>5.523956058999999</v>
       </c>
       <c r="Q36">
-        <v>11.7390561716</v>
+        <v>11.633956059</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1130286179698219</v>
+        <v>0.1139116918930682</v>
       </c>
       <c r="T36">
-        <v>1.55262397158942</v>
+        <v>1.573018288523515</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.575264493439697</v>
+        <v>2.501685507912848</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4529,22 +4529,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09402360973049434</v>
+        <v>0.09515298360090621</v>
       </c>
       <c r="C37">
-        <v>114.8309132794522</v>
+        <v>110.5060559479526</v>
       </c>
       <c r="D37">
-        <v>175.7159132794522</v>
+        <v>173.2320559479526</v>
       </c>
       <c r="E37">
-        <v>39.335</v>
+        <v>41.17600000000001</v>
       </c>
       <c r="F37">
-        <v>64.435</v>
+        <v>66.27600000000001</v>
       </c>
       <c r="G37">
         <v>3.55</v>
@@ -4565,45 +4565,45 @@
         <v>11.59</v>
       </c>
       <c r="M37">
-        <v>4.632876500000001</v>
+        <v>5.023720800000001</v>
       </c>
       <c r="N37">
-        <v>6.957123499999999</v>
+        <v>6.566279199999999</v>
       </c>
       <c r="O37">
-        <v>1.433167441</v>
+        <v>1.3526535152</v>
       </c>
       <c r="P37">
-        <v>5.523956058999999</v>
+        <v>5.213625684799998</v>
       </c>
       <c r="Q37">
-        <v>11.633956059</v>
+        <v>11.3236256848</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1139116918930682</v>
+        <v>0.114822361876416</v>
       </c>
       <c r="T37">
-        <v>1.573018288523515</v>
+        <v>1.5940499278618</v>
       </c>
       <c r="U37">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V37">
         <v>0.206</v>
       </c>
       <c r="W37">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.501685507912848</v>
+        <v>2.307054962130857</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4611,22 +4611,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09515298360090621</v>
+        <v>0.09519854747131809</v>
       </c>
       <c r="C38">
-        <v>110.5060559479526</v>
+        <v>108.5663191405477</v>
       </c>
       <c r="D38">
-        <v>173.2320559479526</v>
+        <v>173.1333191405477</v>
       </c>
       <c r="E38">
-        <v>41.17599999999999</v>
+        <v>43.01699999999999</v>
       </c>
       <c r="F38">
-        <v>66.276</v>
+        <v>68.11699999999999</v>
       </c>
       <c r="G38">
         <v>3.55</v>
@@ -4647,28 +4647,28 @@
         <v>11.59</v>
       </c>
       <c r="M38">
-        <v>5.0237208</v>
+        <v>5.163268599999999</v>
       </c>
       <c r="N38">
-        <v>6.566279199999999</v>
+        <v>6.4267314</v>
       </c>
       <c r="O38">
-        <v>1.3526535152</v>
+        <v>1.3239066684</v>
       </c>
       <c r="P38">
-        <v>5.213625684799999</v>
+        <v>5.1028247316</v>
       </c>
       <c r="Q38">
-        <v>11.3236256848</v>
+        <v>11.2128247316</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.114822361876416</v>
+        <v>0.1157619420179652</v>
       </c>
       <c r="T38">
-        <v>1.5940499278618</v>
+        <v>1.615749238290189</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.307054962130857</v>
+        <v>2.24470212531651</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4693,22 +4693,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09519854747131809</v>
+        <v>0.09524411134172997</v>
       </c>
       <c r="C39">
-        <v>108.5663191405477</v>
+        <v>106.6266948227586</v>
       </c>
       <c r="D39">
-        <v>173.1333191405477</v>
+        <v>173.0346948227586</v>
       </c>
       <c r="E39">
-        <v>43.01699999999999</v>
+        <v>44.858</v>
       </c>
       <c r="F39">
-        <v>68.11699999999999</v>
+        <v>69.958</v>
       </c>
       <c r="G39">
         <v>3.55</v>
@@ -4729,28 +4729,28 @@
         <v>11.59</v>
       </c>
       <c r="M39">
-        <v>5.163268599999999</v>
+        <v>5.3028164</v>
       </c>
       <c r="N39">
-        <v>6.4267314</v>
+        <v>6.2871836</v>
       </c>
       <c r="O39">
-        <v>1.3239066684</v>
+        <v>1.2951598216</v>
       </c>
       <c r="P39">
-        <v>5.1028247316</v>
+        <v>4.9920237784</v>
       </c>
       <c r="Q39">
-        <v>11.2128247316</v>
+        <v>11.1020237784</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1157619420179652</v>
+        <v>0.1167318311963386</v>
       </c>
       <c r="T39">
-        <v>1.615749238290189</v>
+        <v>1.638148526474334</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.24470212531651</v>
+        <v>2.185631016755549</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4775,22 +4775,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09524411134172997</v>
+        <v>0.09528967521214185</v>
       </c>
       <c r="C40">
-        <v>106.6266948227586</v>
+        <v>104.6871828024576</v>
       </c>
       <c r="D40">
-        <v>173.0346948227586</v>
+        <v>172.9361828024576</v>
       </c>
       <c r="E40">
-        <v>44.858</v>
+        <v>46.69900000000001</v>
       </c>
       <c r="F40">
-        <v>69.958</v>
+        <v>71.79900000000001</v>
       </c>
       <c r="G40">
         <v>3.55</v>
@@ -4811,28 +4811,28 @@
         <v>11.59</v>
       </c>
       <c r="M40">
-        <v>5.3028164</v>
+        <v>5.442364200000001</v>
       </c>
       <c r="N40">
-        <v>6.2871836</v>
+        <v>6.147635799999999</v>
       </c>
       <c r="O40">
-        <v>1.2951598216</v>
+        <v>1.2664129748</v>
       </c>
       <c r="P40">
-        <v>4.9920237784</v>
+        <v>4.881222825199999</v>
       </c>
       <c r="Q40">
-        <v>11.1020237784</v>
+        <v>10.9912228252</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1167318311963386</v>
+        <v>0.1177335200199047</v>
       </c>
       <c r="T40">
-        <v>1.638148526474334</v>
+        <v>1.661282217549761</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.185631016755549</v>
+        <v>2.129589195813098</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4857,22 +4857,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09528967521214185</v>
+        <v>0.09533523908255373</v>
       </c>
       <c r="C41">
-        <v>104.6871828024576</v>
+        <v>102.7477828879545</v>
       </c>
       <c r="D41">
-        <v>172.9361828024576</v>
+        <v>172.8377828879545</v>
       </c>
       <c r="E41">
-        <v>46.69900000000001</v>
+        <v>48.54</v>
       </c>
       <c r="F41">
-        <v>71.79900000000001</v>
+        <v>73.64</v>
       </c>
       <c r="G41">
         <v>3.55</v>
@@ -4893,28 +4893,28 @@
         <v>11.59</v>
       </c>
       <c r="M41">
-        <v>5.442364200000001</v>
+        <v>5.581912000000001</v>
       </c>
       <c r="N41">
-        <v>6.147635799999999</v>
+        <v>6.008087999999999</v>
       </c>
       <c r="O41">
-        <v>1.2664129748</v>
+        <v>1.237666128</v>
       </c>
       <c r="P41">
-        <v>4.881222825199999</v>
+        <v>4.770421871999999</v>
       </c>
       <c r="Q41">
-        <v>10.9912228252</v>
+        <v>10.880421872</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1177335200199047</v>
+        <v>0.1187685984709229</v>
       </c>
       <c r="T41">
-        <v>1.661282217549761</v>
+        <v>1.685187031661036</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.129589195813098</v>
+        <v>2.076349465917771</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4939,22 +4939,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09533523908255373</v>
+        <v>0.09538080295296561</v>
       </c>
       <c r="C42">
-        <v>102.7477828879545</v>
+        <v>100.808494887995</v>
       </c>
       <c r="D42">
-        <v>172.8377828879545</v>
+        <v>172.739494887995</v>
       </c>
       <c r="E42">
-        <v>48.54</v>
+        <v>50.38100000000001</v>
       </c>
       <c r="F42">
-        <v>73.64</v>
+        <v>75.48100000000001</v>
       </c>
       <c r="G42">
         <v>3.55</v>
@@ -4975,28 +4975,28 @@
         <v>11.59</v>
       </c>
       <c r="M42">
-        <v>5.581912000000001</v>
+        <v>5.721459800000001</v>
       </c>
       <c r="N42">
-        <v>6.008087999999999</v>
+        <v>5.868540199999999</v>
       </c>
       <c r="O42">
-        <v>1.237666128</v>
+        <v>1.2089192812</v>
       </c>
       <c r="P42">
-        <v>4.770421871999999</v>
+        <v>4.659620918799999</v>
       </c>
       <c r="Q42">
-        <v>10.880421872</v>
+        <v>10.7696209188</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1187685984709229</v>
+        <v>0.1198387643270603</v>
       </c>
       <c r="T42">
-        <v>1.685187031661036</v>
+        <v>1.709902178454049</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.076349465917771</v>
+        <v>2.025706796017338</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5021,22 +5021,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09538080295296561</v>
+        <v>0.1001617828233775</v>
       </c>
       <c r="C43">
-        <v>100.808494887995</v>
+        <v>89.24049284408144</v>
       </c>
       <c r="D43">
-        <v>172.739494887995</v>
+        <v>163.0124928440814</v>
       </c>
       <c r="E43">
-        <v>50.38100000000001</v>
+        <v>52.222</v>
       </c>
       <c r="F43">
-        <v>75.48100000000001</v>
+        <v>77.322</v>
       </c>
       <c r="G43">
         <v>3.55</v>
@@ -5057,45 +5057,45 @@
         <v>11.59</v>
       </c>
       <c r="M43">
-        <v>5.721459800000001</v>
+        <v>6.95898</v>
       </c>
       <c r="N43">
-        <v>5.868540199999999</v>
+        <v>4.631019999999999</v>
       </c>
       <c r="O43">
-        <v>1.2089192812</v>
+        <v>0.9539901199999999</v>
       </c>
       <c r="P43">
-        <v>4.659620918799999</v>
+        <v>3.67702988</v>
       </c>
       <c r="Q43">
-        <v>10.7696209188</v>
+        <v>9.78702988</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1198387643270603</v>
+        <v>0.1209458324540991</v>
       </c>
       <c r="T43">
-        <v>1.709902178454049</v>
+        <v>1.735469571688201</v>
       </c>
       <c r="U43">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V43">
         <v>0.206</v>
       </c>
       <c r="W43">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.025706796017338</v>
+        <v>1.665473963138276</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5103,22 +5103,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1001617828233775</v>
+        <v>0.1003200946937894</v>
       </c>
       <c r="C44">
-        <v>89.2404928440814</v>
+        <v>87.09610666856462</v>
       </c>
       <c r="D44">
-        <v>163.0124928440814</v>
+        <v>162.7091066685646</v>
       </c>
       <c r="E44">
-        <v>52.22199999999999</v>
+        <v>54.063</v>
       </c>
       <c r="F44">
-        <v>77.32199999999999</v>
+        <v>79.163</v>
       </c>
       <c r="G44">
         <v>3.55</v>
@@ -5139,28 +5139,28 @@
         <v>11.59</v>
       </c>
       <c r="M44">
-        <v>6.958979999999999</v>
+        <v>7.124669999999999</v>
       </c>
       <c r="N44">
-        <v>4.631020000000001</v>
+        <v>4.465330000000001</v>
       </c>
       <c r="O44">
-        <v>0.9539901200000004</v>
+        <v>0.9198579800000002</v>
       </c>
       <c r="P44">
-        <v>3.677029880000001</v>
+        <v>3.545472020000001</v>
       </c>
       <c r="Q44">
-        <v>9.787029880000002</v>
+        <v>9.655472020000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1209458324540991</v>
+        <v>0.1220917450768234</v>
       </c>
       <c r="T44">
-        <v>1.7354695716882</v>
+        <v>1.76193406643934</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.665473963138276</v>
+        <v>1.626742010507154</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5185,22 +5185,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1003200946937894</v>
+        <v>0.1004784065642012</v>
       </c>
       <c r="C45">
-        <v>87.09610666856462</v>
+        <v>84.9528476727446</v>
       </c>
       <c r="D45">
-        <v>162.7091066685646</v>
+        <v>162.4068476727446</v>
       </c>
       <c r="E45">
-        <v>54.063</v>
+        <v>55.904</v>
       </c>
       <c r="F45">
-        <v>79.163</v>
+        <v>81.004</v>
       </c>
       <c r="G45">
         <v>3.55</v>
@@ -5221,28 +5221,28 @@
         <v>11.59</v>
       </c>
       <c r="M45">
-        <v>7.124669999999999</v>
+        <v>7.29036</v>
       </c>
       <c r="N45">
-        <v>4.465330000000001</v>
+        <v>4.29964</v>
       </c>
       <c r="O45">
-        <v>0.9198579800000002</v>
+        <v>0.8857258400000001</v>
       </c>
       <c r="P45">
-        <v>3.545472020000001</v>
+        <v>3.41391416</v>
       </c>
       <c r="Q45">
-        <v>9.655472020000001</v>
+        <v>9.52391416</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1220917450768234</v>
+        <v>0.1232785831503593</v>
       </c>
       <c r="T45">
-        <v>1.76193406643934</v>
+        <v>1.789343721717306</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.626742010507154</v>
+        <v>1.589770601177445</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5267,22 +5267,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1004784065642012</v>
+        <v>0.1006367184346131</v>
       </c>
       <c r="C46">
-        <v>84.9528476727446</v>
+        <v>82.81070958650264</v>
       </c>
       <c r="D46">
-        <v>162.4068476727446</v>
+        <v>162.1057095865026</v>
       </c>
       <c r="E46">
-        <v>55.904</v>
+        <v>57.745</v>
       </c>
       <c r="F46">
-        <v>81.004</v>
+        <v>82.845</v>
       </c>
       <c r="G46">
         <v>3.55</v>
@@ -5303,28 +5303,28 @@
         <v>11.59</v>
       </c>
       <c r="M46">
-        <v>7.29036</v>
+        <v>7.456049999999999</v>
       </c>
       <c r="N46">
-        <v>4.29964</v>
+        <v>4.13395</v>
       </c>
       <c r="O46">
-        <v>0.8857258400000001</v>
+        <v>0.8515937000000001</v>
       </c>
       <c r="P46">
-        <v>3.41391416</v>
+        <v>3.2823563</v>
       </c>
       <c r="Q46">
-        <v>9.52391416</v>
+        <v>9.392356300000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1232785831503593</v>
+        <v>0.1245085789720238</v>
       </c>
       <c r="T46">
-        <v>1.789343721717306</v>
+        <v>1.817750091732652</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.589770601177445</v>
+        <v>1.554442365595724</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1006367184346131</v>
+        <v>0.100795030305025</v>
       </c>
       <c r="C47">
-        <v>82.81070958650264</v>
+        <v>80.6696861861387</v>
       </c>
       <c r="D47">
-        <v>162.1057095865026</v>
+        <v>161.8056861861387</v>
       </c>
       <c r="E47">
-        <v>57.745</v>
+        <v>59.58600000000001</v>
       </c>
       <c r="F47">
-        <v>82.845</v>
+        <v>84.68600000000001</v>
       </c>
       <c r="G47">
         <v>3.55</v>
@@ -5385,28 +5385,28 @@
         <v>11.59</v>
       </c>
       <c r="M47">
-        <v>7.456049999999999</v>
+        <v>7.62174</v>
       </c>
       <c r="N47">
-        <v>4.13395</v>
+        <v>3.96826</v>
       </c>
       <c r="O47">
-        <v>0.8515937000000001</v>
+        <v>0.81746156</v>
       </c>
       <c r="P47">
-        <v>3.2823563</v>
+        <v>3.15079844</v>
       </c>
       <c r="Q47">
-        <v>9.392356300000001</v>
+        <v>9.26079844</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1245085789720238</v>
+        <v>0.1257841301944907</v>
       </c>
       <c r="T47">
-        <v>1.817750091732652</v>
+        <v>1.847208549526344</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.554442365595724</v>
+        <v>1.520650140256687</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5431,22 +5431,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.100795030305025</v>
+        <v>0.1237989028612684</v>
       </c>
       <c r="C48">
-        <v>80.6696861861387</v>
+        <v>44.53617121669687</v>
       </c>
       <c r="D48">
-        <v>161.8056861861387</v>
+        <v>127.5131712166969</v>
       </c>
       <c r="E48">
-        <v>59.58600000000001</v>
+        <v>61.427</v>
       </c>
       <c r="F48">
-        <v>84.68600000000001</v>
+        <v>86.527</v>
       </c>
       <c r="G48">
         <v>3.55</v>
@@ -5467,45 +5467,45 @@
         <v>11.59</v>
       </c>
       <c r="M48">
-        <v>7.62174</v>
+        <v>12.7021636</v>
       </c>
       <c r="N48">
-        <v>3.96826</v>
+        <v>-1.112163600000002</v>
       </c>
       <c r="O48">
-        <v>0.81746156</v>
+        <v>-0.2291057016000005</v>
       </c>
       <c r="P48">
-        <v>3.15079844</v>
+        <v>-0.8830578984000018</v>
       </c>
       <c r="Q48">
-        <v>9.26079844</v>
+        <v>5.226942101599999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1257841301944907</v>
+        <v>0.1278709726744028</v>
       </c>
       <c r="T48">
-        <v>1.847208549526344</v>
+        <v>1.895403525967731</v>
       </c>
       <c r="U48">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.206</v>
+        <v>0.1879632537562341</v>
       </c>
       <c r="W48">
-        <v>0.07146</v>
+        <v>0.1192069943485848</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.520650140256687</v>
+        <v>0.9124429793991945</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1237989028612684</v>
+        <v>0.1248089028612684</v>
       </c>
       <c r="C49">
-        <v>44.53617121669687</v>
+        <v>41.51957410156221</v>
       </c>
       <c r="D49">
-        <v>127.5131712166969</v>
+        <v>126.3375741015622</v>
       </c>
       <c r="E49">
-        <v>61.427</v>
+        <v>63.26800000000001</v>
       </c>
       <c r="F49">
-        <v>86.527</v>
+        <v>88.36800000000001</v>
       </c>
       <c r="G49">
         <v>3.55</v>
@@ -5549,37 +5549,37 @@
         <v>11.59</v>
       </c>
       <c r="M49">
-        <v>12.7021636</v>
+        <v>12.9724224</v>
       </c>
       <c r="N49">
-        <v>-1.112163600000002</v>
+        <v>-1.382422400000003</v>
       </c>
       <c r="O49">
-        <v>-0.2291057016000005</v>
+        <v>-0.2847790144000006</v>
       </c>
       <c r="P49">
-        <v>-0.8830578984000018</v>
+        <v>-1.097643385600002</v>
       </c>
       <c r="Q49">
-        <v>5.226942101599999</v>
+        <v>5.012356614399998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1278709726744028</v>
+        <v>0.129449260610449</v>
       </c>
       <c r="T49">
-        <v>1.895403525967731</v>
+        <v>1.931853593774803</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1879632537562341</v>
+        <v>0.1840473526363125</v>
       </c>
       <c r="W49">
-        <v>0.1192069943485848</v>
+        <v>0.1197818486329893</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9124429793991945</v>
+        <v>0.8934337506617112</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5595,22 +5595,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1248089028612684</v>
+        <v>0.1258189028612683</v>
       </c>
       <c r="C50">
-        <v>41.51957410156223</v>
+        <v>38.5244556064351</v>
       </c>
       <c r="D50">
-        <v>126.3375741015622</v>
+        <v>125.1834556064351</v>
       </c>
       <c r="E50">
-        <v>63.26799999999999</v>
+        <v>65.10899999999998</v>
       </c>
       <c r="F50">
-        <v>88.36799999999999</v>
+        <v>90.20899999999999</v>
       </c>
       <c r="G50">
         <v>3.55</v>
@@ -5631,37 +5631,37 @@
         <v>11.59</v>
       </c>
       <c r="M50">
-        <v>12.9724224</v>
+        <v>13.2426812</v>
       </c>
       <c r="N50">
-        <v>-1.382422400000001</v>
+        <v>-1.6526812</v>
       </c>
       <c r="O50">
-        <v>-0.2847790144000003</v>
+        <v>-0.3404523272</v>
       </c>
       <c r="P50">
-        <v>-1.097643385600001</v>
+        <v>-1.3122288728</v>
       </c>
       <c r="Q50">
-        <v>5.0123566144</v>
+        <v>4.797771127200001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.129449260610449</v>
+        <v>0.131089442191046</v>
       </c>
       <c r="T50">
-        <v>1.931853593774803</v>
+        <v>1.969733076005681</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1840473526363126</v>
+        <v>0.1802912842151633</v>
       </c>
       <c r="W50">
-        <v>0.1197818486329893</v>
+        <v>0.120333239477214</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8934337506617114</v>
+        <v>0.8752004088114724</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5677,22 +5677,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1258189028612683</v>
+        <v>0.1268289028612684</v>
       </c>
       <c r="C51">
-        <v>38.5244556064351</v>
+        <v>35.55023242571882</v>
       </c>
       <c r="D51">
-        <v>125.1834556064351</v>
+        <v>124.0502324257188</v>
       </c>
       <c r="E51">
-        <v>65.10899999999998</v>
+        <v>66.94999999999999</v>
       </c>
       <c r="F51">
-        <v>90.20899999999999</v>
+        <v>92.05</v>
       </c>
       <c r="G51">
         <v>3.55</v>
@@ -5713,37 +5713,37 @@
         <v>11.59</v>
       </c>
       <c r="M51">
-        <v>13.2426812</v>
+        <v>13.51294</v>
       </c>
       <c r="N51">
-        <v>-1.6526812</v>
+        <v>-1.922940000000001</v>
       </c>
       <c r="O51">
-        <v>-0.3404523272</v>
+        <v>-0.3961256400000002</v>
       </c>
       <c r="P51">
-        <v>-1.3122288728</v>
+        <v>-1.52681436</v>
       </c>
       <c r="Q51">
-        <v>4.797771127200001</v>
+        <v>4.58318564</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.131089442191046</v>
+        <v>0.132795231034867</v>
       </c>
       <c r="T51">
-        <v>1.969733076005681</v>
+        <v>2.009127737525795</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1802912842151633</v>
+        <v>0.17668545853086</v>
       </c>
       <c r="W51">
-        <v>0.120333239477214</v>
+        <v>0.1208625746876698</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8752004088114724</v>
+        <v>0.8576964006352429</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5759,22 +5759,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1268289028612684</v>
+        <v>0.1278389028612684</v>
       </c>
       <c r="C52">
-        <v>35.55023242571882</v>
+        <v>32.59634218582462</v>
       </c>
       <c r="D52">
-        <v>124.0502324257188</v>
+        <v>122.9373421858246</v>
       </c>
       <c r="E52">
-        <v>66.94999999999999</v>
+        <v>68.791</v>
       </c>
       <c r="F52">
-        <v>92.05</v>
+        <v>93.89100000000001</v>
       </c>
       <c r="G52">
         <v>3.55</v>
@@ -5795,37 +5795,37 @@
         <v>11.59</v>
       </c>
       <c r="M52">
-        <v>13.51294</v>
+        <v>13.7831988</v>
       </c>
       <c r="N52">
-        <v>-1.922940000000001</v>
+        <v>-2.193198800000003</v>
       </c>
       <c r="O52">
-        <v>-0.3961256400000002</v>
+        <v>-0.4517989528000007</v>
       </c>
       <c r="P52">
-        <v>-1.52681436</v>
+        <v>-1.741399847200002</v>
       </c>
       <c r="Q52">
-        <v>4.58318564</v>
+        <v>4.368600152799998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.132795231034867</v>
+        <v>0.1345706439131295</v>
       </c>
       <c r="T52">
-        <v>2.009127737525795</v>
+        <v>2.050130344414077</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.17668545853086</v>
+        <v>0.173221037775353</v>
       </c>
       <c r="W52">
-        <v>0.1208625746876698</v>
+        <v>0.1213711516545782</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8576964006352429</v>
+        <v>0.8408788241521988</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5841,22 +5841,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1278389028612684</v>
+        <v>0.1288489028612683</v>
       </c>
       <c r="C53">
-        <v>32.59634218582462</v>
+        <v>29.66224251458485</v>
       </c>
       <c r="D53">
-        <v>122.9373421858246</v>
+        <v>121.8442425145848</v>
       </c>
       <c r="E53">
-        <v>68.791</v>
+        <v>70.63200000000001</v>
       </c>
       <c r="F53">
-        <v>93.89100000000001</v>
+        <v>95.732</v>
       </c>
       <c r="G53">
         <v>3.55</v>
@@ -5877,37 +5877,37 @@
         <v>11.59</v>
       </c>
       <c r="M53">
-        <v>13.7831988</v>
+        <v>14.0534576</v>
       </c>
       <c r="N53">
-        <v>-2.193198800000003</v>
+        <v>-2.463457600000002</v>
       </c>
       <c r="O53">
-        <v>-0.4517989528000007</v>
+        <v>-0.5074722656000004</v>
       </c>
       <c r="P53">
-        <v>-1.741399847200002</v>
+        <v>-1.955985334400001</v>
       </c>
       <c r="Q53">
-        <v>4.368600152799998</v>
+        <v>4.154014665599999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1345706439131295</v>
+        <v>0.1364200323279864</v>
       </c>
       <c r="T53">
-        <v>2.050130344414077</v>
+        <v>2.092841393256037</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.173221037775353</v>
+        <v>0.1698898639719808</v>
       </c>
       <c r="W53">
-        <v>0.1213711516545782</v>
+        <v>0.1218601679689132</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8408788241521988</v>
+        <v>0.8247080775338873</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5923,22 +5923,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1288489028612683</v>
+        <v>0.1298589028612683</v>
       </c>
       <c r="C54">
-        <v>29.66224251458485</v>
+        <v>26.74741015987433</v>
       </c>
       <c r="D54">
-        <v>121.8442425145848</v>
+        <v>120.7704101598743</v>
       </c>
       <c r="E54">
-        <v>70.63200000000001</v>
+        <v>72.47300000000001</v>
       </c>
       <c r="F54">
-        <v>95.732</v>
+        <v>97.57300000000001</v>
       </c>
       <c r="G54">
         <v>3.55</v>
@@ -5959,37 +5959,37 @@
         <v>11.59</v>
       </c>
       <c r="M54">
-        <v>14.0534576</v>
+        <v>14.3237164</v>
       </c>
       <c r="N54">
-        <v>-2.463457600000002</v>
+        <v>-2.733716400000002</v>
       </c>
       <c r="O54">
-        <v>-0.5074722656000004</v>
+        <v>-0.5631455784000005</v>
       </c>
       <c r="P54">
-        <v>-1.955985334400001</v>
+        <v>-2.170570821600002</v>
       </c>
       <c r="Q54">
-        <v>4.154014665599999</v>
+        <v>3.939429178399998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1364200323279864</v>
+        <v>0.1383481181221989</v>
       </c>
       <c r="T54">
-        <v>2.092841393256037</v>
+        <v>2.13736993353808</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1698898639719808</v>
+        <v>0.166684394840434</v>
       </c>
       <c r="W54">
-        <v>0.1218601679689132</v>
+        <v>0.1223307308374243</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8247080775338873</v>
+        <v>0.809147547769097</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6005,22 +6005,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1298589028612683</v>
+        <v>0.1611624372857048</v>
       </c>
       <c r="C55">
-        <v>26.74741015987433</v>
+        <v>-1.004576731885734</v>
       </c>
       <c r="D55">
-        <v>120.7704101598743</v>
+        <v>94.85942326811427</v>
       </c>
       <c r="E55">
-        <v>72.47300000000001</v>
+        <v>74.31399999999999</v>
       </c>
       <c r="F55">
-        <v>97.57300000000001</v>
+        <v>99.414</v>
       </c>
       <c r="G55">
         <v>3.55</v>
@@ -6041,45 +6041,45 @@
         <v>11.59</v>
       </c>
       <c r="M55">
-        <v>14.3237164</v>
+        <v>19.9623312</v>
       </c>
       <c r="N55">
-        <v>-2.733716400000002</v>
+        <v>-8.372331200000001</v>
       </c>
       <c r="O55">
-        <v>-0.5631455784000005</v>
+        <v>-1.7247002272</v>
       </c>
       <c r="P55">
-        <v>-2.170570821600002</v>
+        <v>-6.647630972800001</v>
       </c>
       <c r="Q55">
-        <v>3.939429178399998</v>
+        <v>-0.5376309728000006</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1383481181221989</v>
+        <v>0.142824239004065</v>
       </c>
       <c r="T55">
-        <v>2.13736993353808</v>
+        <v>2.24074454974746</v>
       </c>
       <c r="U55">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.166684394840434</v>
+        <v>0.1196022636875196</v>
       </c>
       <c r="W55">
-        <v>0.1223307308374243</v>
+        <v>0.1767838654515461</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.809147547769097</v>
+        <v>0.5805935130462117</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6087,22 +6087,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1611624372857048</v>
+        <v>0.1627124372857048</v>
       </c>
       <c r="C56">
-        <v>-1.004576731885734</v>
+        <v>-3.842709262354461</v>
       </c>
       <c r="D56">
-        <v>94.85942326811427</v>
+        <v>93.86229073764555</v>
       </c>
       <c r="E56">
-        <v>74.31399999999999</v>
+        <v>76.155</v>
       </c>
       <c r="F56">
-        <v>99.414</v>
+        <v>101.255</v>
       </c>
       <c r="G56">
         <v>3.55</v>
@@ -6123,37 +6123,37 @@
         <v>11.59</v>
       </c>
       <c r="M56">
-        <v>19.9623312</v>
+        <v>20.332004</v>
       </c>
       <c r="N56">
-        <v>-8.372331200000001</v>
+        <v>-8.742004000000001</v>
       </c>
       <c r="O56">
-        <v>-1.7247002272</v>
+        <v>-1.800852824</v>
       </c>
       <c r="P56">
-        <v>-6.647630972800001</v>
+        <v>-6.941151176000001</v>
       </c>
       <c r="Q56">
-        <v>-0.5376309728000006</v>
+        <v>-0.8311511760000005</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.142824239004065</v>
+        <v>0.1449803332041554</v>
       </c>
       <c r="T56">
-        <v>2.24074454974746</v>
+        <v>2.290538873075182</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1196022636875196</v>
+        <v>0.1174276770750193</v>
       </c>
       <c r="W56">
-        <v>0.1767838654515461</v>
+        <v>0.1772205224433361</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5805935130462117</v>
+        <v>0.5700372673544625</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6169,22 +6169,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1627124372857048</v>
+        <v>0.1642624372857048</v>
       </c>
       <c r="C57">
-        <v>-3.842709262354461</v>
+        <v>-6.660096768655876</v>
       </c>
       <c r="D57">
-        <v>93.86229073764555</v>
+        <v>92.88590323134413</v>
       </c>
       <c r="E57">
-        <v>76.155</v>
+        <v>77.99600000000001</v>
       </c>
       <c r="F57">
-        <v>101.255</v>
+        <v>103.096</v>
       </c>
       <c r="G57">
         <v>3.55</v>
@@ -6205,37 +6205,37 @@
         <v>11.59</v>
       </c>
       <c r="M57">
-        <v>20.332004</v>
+        <v>20.7016768</v>
       </c>
       <c r="N57">
-        <v>-8.742004000000001</v>
+        <v>-9.111676800000001</v>
       </c>
       <c r="O57">
-        <v>-1.800852824</v>
+        <v>-1.8770054208</v>
       </c>
       <c r="P57">
-        <v>-6.941151176000001</v>
+        <v>-7.234671379200001</v>
       </c>
       <c r="Q57">
-        <v>-0.8311511760000005</v>
+        <v>-1.1246713792</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1449803332041554</v>
+        <v>0.147234431686068</v>
       </c>
       <c r="T57">
-        <v>2.290538873075182</v>
+        <v>2.342596574735981</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1174276770750193</v>
+        <v>0.1153307542701082</v>
       </c>
       <c r="W57">
-        <v>0.1772205224433361</v>
+        <v>0.1776415845425623</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5700372673544625</v>
+        <v>0.5598580304374184</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6251,22 +6251,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1642624372857048</v>
+        <v>0.1658124372857048</v>
       </c>
       <c r="C58">
-        <v>-6.660096768655876</v>
+        <v>-9.457379976160368</v>
       </c>
       <c r="D58">
-        <v>92.88590323134413</v>
+        <v>91.92962002383965</v>
       </c>
       <c r="E58">
-        <v>77.99600000000001</v>
+        <v>79.83700000000002</v>
       </c>
       <c r="F58">
-        <v>103.096</v>
+        <v>104.937</v>
       </c>
       <c r="G58">
         <v>3.55</v>
@@ -6287,37 +6287,37 @@
         <v>11.59</v>
       </c>
       <c r="M58">
-        <v>20.7016768</v>
+        <v>21.0713496</v>
       </c>
       <c r="N58">
-        <v>-9.111676800000001</v>
+        <v>-9.481349600000001</v>
       </c>
       <c r="O58">
-        <v>-1.8770054208</v>
+        <v>-1.953158017600001</v>
       </c>
       <c r="P58">
-        <v>-7.234671379200001</v>
+        <v>-7.528191582400001</v>
       </c>
       <c r="Q58">
-        <v>-1.1246713792</v>
+        <v>-1.4181915824</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.147234431686068</v>
+        <v>0.149593371957837</v>
       </c>
       <c r="T58">
-        <v>2.342596574735981</v>
+        <v>2.39707556484612</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1153307542701082</v>
+        <v>0.113307407703966</v>
       </c>
       <c r="W58">
-        <v>0.1776415845425623</v>
+        <v>0.1780478725330436</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5598580304374184</v>
+        <v>0.55003595972799</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6333,22 +6333,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1658124372857048</v>
+        <v>0.1673624372857048</v>
       </c>
       <c r="C59">
-        <v>-9.457379976160368</v>
+        <v>-12.23517349341664</v>
       </c>
       <c r="D59">
-        <v>91.92962002383965</v>
+        <v>90.99282650658337</v>
       </c>
       <c r="E59">
-        <v>79.83700000000002</v>
+        <v>81.678</v>
       </c>
       <c r="F59">
-        <v>104.937</v>
+        <v>106.778</v>
       </c>
       <c r="G59">
         <v>3.55</v>
@@ -6369,37 +6369,37 @@
         <v>11.59</v>
       </c>
       <c r="M59">
-        <v>21.0713496</v>
+        <v>21.4410224</v>
       </c>
       <c r="N59">
-        <v>-9.481349600000001</v>
+        <v>-9.851022400000002</v>
       </c>
       <c r="O59">
-        <v>-1.953158017600001</v>
+        <v>-2.0293106144</v>
       </c>
       <c r="P59">
-        <v>-7.528191582400001</v>
+        <v>-7.821711785600002</v>
       </c>
       <c r="Q59">
-        <v>-1.4181915824</v>
+        <v>-1.711711785600001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.149593371957837</v>
+        <v>0.1520646427187379</v>
       </c>
       <c r="T59">
-        <v>2.39707556484612</v>
+        <v>2.454148792580551</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.113307407703966</v>
+        <v>0.11135383170907</v>
       </c>
       <c r="W59">
-        <v>0.1780478725330436</v>
+        <v>0.1784401505928188</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.55003595972799</v>
+        <v>0.5405525811119902</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6415,22 +6415,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1673624372857048</v>
+        <v>0.1689124372857048</v>
       </c>
       <c r="C60">
-        <v>-12.2351734934166</v>
+        <v>-14.99406712942383</v>
       </c>
       <c r="D60">
-        <v>90.9928265065834</v>
+        <v>90.07493287057616</v>
       </c>
       <c r="E60">
-        <v>81.678</v>
+        <v>83.51899999999998</v>
       </c>
       <c r="F60">
-        <v>106.778</v>
+        <v>108.619</v>
       </c>
       <c r="G60">
         <v>3.55</v>
@@ -6451,37 +6451,37 @@
         <v>11.59</v>
       </c>
       <c r="M60">
-        <v>21.4410224</v>
+        <v>21.8106952</v>
       </c>
       <c r="N60">
-        <v>-9.851022399999998</v>
+        <v>-10.2206952</v>
       </c>
       <c r="O60">
-        <v>-2.0293106144</v>
+        <v>-2.1054632112</v>
       </c>
       <c r="P60">
-        <v>-7.821711785599998</v>
+        <v>-8.115231988799998</v>
       </c>
       <c r="Q60">
-        <v>-1.711711785599998</v>
+        <v>-2.005231988799998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1520646427187379</v>
+        <v>0.1546564632728534</v>
       </c>
       <c r="T60">
-        <v>2.454148792580551</v>
+        <v>2.514006080204467</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.11135383170907</v>
+        <v>0.1094664786292553</v>
       </c>
       <c r="W60">
-        <v>0.1784401505928188</v>
+        <v>0.1788191310912455</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5405525811119902</v>
+        <v>0.5313906729575497</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6497,22 +6497,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1689124372857048</v>
+        <v>0.1704624372857048</v>
       </c>
       <c r="C61">
-        <v>-14.99406712942383</v>
+        <v>-17.73462713197212</v>
       </c>
       <c r="D61">
-        <v>90.07493287057616</v>
+        <v>89.17537286802788</v>
       </c>
       <c r="E61">
-        <v>83.51899999999998</v>
+        <v>85.35999999999999</v>
       </c>
       <c r="F61">
-        <v>108.619</v>
+        <v>110.46</v>
       </c>
       <c r="G61">
         <v>3.55</v>
@@ -6533,37 +6533,37 @@
         <v>11.59</v>
       </c>
       <c r="M61">
-        <v>21.8106952</v>
+        <v>22.180368</v>
       </c>
       <c r="N61">
-        <v>-10.2206952</v>
+        <v>-10.590368</v>
       </c>
       <c r="O61">
-        <v>-2.1054632112</v>
+        <v>-2.181615808</v>
       </c>
       <c r="P61">
-        <v>-8.115231988799998</v>
+        <v>-8.408752191999998</v>
       </c>
       <c r="Q61">
-        <v>-2.005231988799998</v>
+        <v>-2.298752191999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1546564632728534</v>
+        <v>0.1573778748546748</v>
       </c>
       <c r="T61">
-        <v>2.514006080204467</v>
+        <v>2.576856232209579</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1094664786292553</v>
+        <v>0.1076420373187677</v>
       </c>
       <c r="W61">
-        <v>0.1788191310912455</v>
+        <v>0.1791854789063915</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5313906729575497</v>
+        <v>0.5225341617415906</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1704624372857048</v>
+        <v>0.1720124372857048</v>
       </c>
       <c r="C62">
-        <v>-17.73462713197212</v>
+        <v>-20.45739735251382</v>
       </c>
       <c r="D62">
-        <v>89.17537286802788</v>
+        <v>88.29360264748617</v>
       </c>
       <c r="E62">
-        <v>85.35999999999999</v>
+        <v>87.20099999999999</v>
       </c>
       <c r="F62">
-        <v>110.46</v>
+        <v>112.301</v>
       </c>
       <c r="G62">
         <v>3.55</v>
@@ -6615,37 +6615,37 @@
         <v>11.59</v>
       </c>
       <c r="M62">
-        <v>22.180368</v>
+        <v>22.5500408</v>
       </c>
       <c r="N62">
-        <v>-10.590368</v>
+        <v>-10.9600408</v>
       </c>
       <c r="O62">
-        <v>-2.181615808</v>
+        <v>-2.2577684048</v>
       </c>
       <c r="P62">
-        <v>-8.408752191999998</v>
+        <v>-8.702272395199998</v>
       </c>
       <c r="Q62">
-        <v>-2.298752191999998</v>
+        <v>-2.592272395199998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1573778748546748</v>
+        <v>0.1602388460047946</v>
       </c>
       <c r="T62">
-        <v>2.576856232209579</v>
+        <v>2.642929468932901</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1076420373187677</v>
+        <v>0.1058774137561649</v>
       </c>
       <c r="W62">
-        <v>0.1791854789063915</v>
+        <v>0.1795398153177621</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5225341617415906</v>
+        <v>0.5139680279425481</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6661,22 +6661,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1720124372857048</v>
+        <v>0.1735624372857048</v>
       </c>
       <c r="C63">
-        <v>-20.45739735251382</v>
+        <v>-23.16290034260236</v>
       </c>
       <c r="D63">
-        <v>88.29360264748617</v>
+        <v>87.42909965739764</v>
       </c>
       <c r="E63">
-        <v>87.20099999999999</v>
+        <v>89.042</v>
       </c>
       <c r="F63">
-        <v>112.301</v>
+        <v>114.142</v>
       </c>
       <c r="G63">
         <v>3.55</v>
@@ -6697,37 +6697,37 @@
         <v>11.59</v>
       </c>
       <c r="M63">
-        <v>22.5500408</v>
+        <v>22.9197136</v>
       </c>
       <c r="N63">
-        <v>-10.9600408</v>
+        <v>-11.3297136</v>
       </c>
       <c r="O63">
-        <v>-2.2577684048</v>
+        <v>-2.333921001600001</v>
       </c>
       <c r="P63">
-        <v>-8.702272395199998</v>
+        <v>-8.995792598400001</v>
       </c>
       <c r="Q63">
-        <v>-2.592272395199998</v>
+        <v>-2.885792598400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1602388460047946</v>
+        <v>0.1632503945838682</v>
       </c>
       <c r="T63">
-        <v>2.642929468932901</v>
+        <v>2.712480244431136</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1058774137561649</v>
+        <v>0.1041697135342913</v>
       </c>
       <c r="W63">
-        <v>0.1795398153177621</v>
+        <v>0.1798827215223143</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5139680279425481</v>
+        <v>0.5056782210402488</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6743,22 +6743,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1735624372857048</v>
+        <v>0.1976198321175424</v>
       </c>
       <c r="C64">
-        <v>-23.16290034260236</v>
+        <v>-36.53762250018927</v>
       </c>
       <c r="D64">
-        <v>87.42909965739764</v>
+        <v>75.89537749981073</v>
       </c>
       <c r="E64">
-        <v>89.042</v>
+        <v>90.88300000000001</v>
       </c>
       <c r="F64">
-        <v>114.142</v>
+        <v>115.983</v>
       </c>
       <c r="G64">
         <v>3.55</v>
@@ -6779,45 +6779,45 @@
         <v>11.59</v>
       </c>
       <c r="M64">
-        <v>22.9197136</v>
+        <v>27.3487914</v>
       </c>
       <c r="N64">
-        <v>-11.3297136</v>
+        <v>-15.7587914</v>
       </c>
       <c r="O64">
-        <v>-2.333921001600001</v>
+        <v>-3.246311028400001</v>
       </c>
       <c r="P64">
-        <v>-8.995792598400001</v>
+        <v>-12.5124803716</v>
       </c>
       <c r="Q64">
-        <v>-2.885792598400001</v>
+        <v>-6.402480371600002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1632503945838682</v>
+        <v>0.1676609318208311</v>
       </c>
       <c r="T64">
-        <v>2.712480244431136</v>
+        <v>2.814340226809032</v>
       </c>
       <c r="U64">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1041697135342913</v>
+        <v>0.08729965302963991</v>
       </c>
       <c r="W64">
-        <v>0.1798827215223143</v>
+        <v>0.2152147418156109</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5056782210402488</v>
+        <v>0.4237847234448539</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6825,22 +6825,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1976198321175424</v>
+        <v>0.1995198321175424</v>
       </c>
       <c r="C65">
-        <v>-36.53762250018927</v>
+        <v>-39.16120905711082</v>
       </c>
       <c r="D65">
-        <v>75.89537749981073</v>
+        <v>75.11279094288918</v>
       </c>
       <c r="E65">
-        <v>90.88300000000001</v>
+        <v>92.72399999999999</v>
       </c>
       <c r="F65">
-        <v>115.983</v>
+        <v>117.824</v>
       </c>
       <c r="G65">
         <v>3.55</v>
@@ -6861,37 +6861,37 @@
         <v>11.59</v>
       </c>
       <c r="M65">
-        <v>27.3487914</v>
+        <v>27.7828992</v>
       </c>
       <c r="N65">
-        <v>-15.7587914</v>
+        <v>-16.1928992</v>
       </c>
       <c r="O65">
-        <v>-3.246311028400001</v>
+        <v>-3.3357372352</v>
       </c>
       <c r="P65">
-        <v>-12.5124803716</v>
+        <v>-12.8571619648</v>
       </c>
       <c r="Q65">
-        <v>-6.402480371600002</v>
+        <v>-6.747161964799999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1676609318208311</v>
+        <v>0.1710459577047431</v>
       </c>
       <c r="T65">
-        <v>2.814340226809032</v>
+        <v>2.892516344220394</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08729965302963991</v>
+        <v>0.0859355959510518</v>
       </c>
       <c r="W65">
-        <v>0.2152147418156109</v>
+        <v>0.215536386474742</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4237847234448539</v>
+        <v>0.4171630871410281</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6907,22 +6907,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1995198321175424</v>
+        <v>0.2014198321175424</v>
       </c>
       <c r="C66">
-        <v>-39.16120905711082</v>
+        <v>-41.76882122747668</v>
       </c>
       <c r="D66">
-        <v>75.11279094288918</v>
+        <v>74.34617877252333</v>
       </c>
       <c r="E66">
-        <v>92.72399999999999</v>
+        <v>94.565</v>
       </c>
       <c r="F66">
-        <v>117.824</v>
+        <v>119.665</v>
       </c>
       <c r="G66">
         <v>3.55</v>
@@ -6943,37 +6943,37 @@
         <v>11.59</v>
       </c>
       <c r="M66">
-        <v>27.7828992</v>
+        <v>28.217007</v>
       </c>
       <c r="N66">
-        <v>-16.1928992</v>
+        <v>-16.627007</v>
       </c>
       <c r="O66">
-        <v>-3.3357372352</v>
+        <v>-3.425163442000001</v>
       </c>
       <c r="P66">
-        <v>-12.8571619648</v>
+        <v>-13.201843558</v>
       </c>
       <c r="Q66">
-        <v>-6.747161964799999</v>
+        <v>-7.091843558000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1710459577047431</v>
+        <v>0.1746244136391643</v>
       </c>
       <c r="T66">
-        <v>2.892516344220394</v>
+        <v>2.975159668340976</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0859355959510518</v>
+        <v>0.08461350985949714</v>
       </c>
       <c r="W66">
-        <v>0.215536386474742</v>
+        <v>0.2158481343751306</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4171630871410281</v>
+        <v>0.4107451934927046</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6989,22 +6989,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2014198321175424</v>
+        <v>0.2033198321175424</v>
       </c>
       <c r="C67">
-        <v>-41.76882122747668</v>
+        <v>-44.36094318058615</v>
       </c>
       <c r="D67">
-        <v>74.34617877252333</v>
+        <v>73.59505681941386</v>
       </c>
       <c r="E67">
-        <v>94.565</v>
+        <v>96.40600000000001</v>
       </c>
       <c r="F67">
-        <v>119.665</v>
+        <v>121.506</v>
       </c>
       <c r="G67">
         <v>3.55</v>
@@ -7025,37 +7025,37 @@
         <v>11.59</v>
       </c>
       <c r="M67">
-        <v>28.217007</v>
+        <v>28.6511148</v>
       </c>
       <c r="N67">
-        <v>-16.627007</v>
+        <v>-17.0611148</v>
       </c>
       <c r="O67">
-        <v>-3.425163442000001</v>
+        <v>-3.514589648800001</v>
       </c>
       <c r="P67">
-        <v>-13.201843558</v>
+        <v>-13.5465251512</v>
       </c>
       <c r="Q67">
-        <v>-7.091843558000002</v>
+        <v>-7.436525151200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1746244136391643</v>
+        <v>0.1784133669814927</v>
       </c>
       <c r="T67">
-        <v>2.975159668340976</v>
+        <v>3.062664364468652</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08461350985949714</v>
+        <v>0.0833314869828381</v>
       </c>
       <c r="W67">
-        <v>0.2158481343751306</v>
+        <v>0.2161504353694468</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4107451934927046</v>
+        <v>0.4045217814700878</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7071,22 +7071,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2033198321175424</v>
+        <v>0.2052198321175424</v>
       </c>
       <c r="C68">
-        <v>-44.36094318058615</v>
+        <v>-46.93803971512556</v>
       </c>
       <c r="D68">
-        <v>73.59505681941386</v>
+        <v>72.85896028487446</v>
       </c>
       <c r="E68">
-        <v>96.40600000000001</v>
+        <v>98.24700000000001</v>
       </c>
       <c r="F68">
-        <v>121.506</v>
+        <v>123.347</v>
       </c>
       <c r="G68">
         <v>3.55</v>
@@ -7107,37 +7107,37 @@
         <v>11.59</v>
       </c>
       <c r="M68">
-        <v>28.6511148</v>
+        <v>29.0852226</v>
       </c>
       <c r="N68">
-        <v>-17.0611148</v>
+        <v>-17.4952226</v>
       </c>
       <c r="O68">
-        <v>-3.514589648800001</v>
+        <v>-3.604015855600001</v>
       </c>
       <c r="P68">
-        <v>-13.5465251512</v>
+        <v>-13.8912067444</v>
       </c>
       <c r="Q68">
-        <v>-7.436525151200001</v>
+        <v>-7.781206744400001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1784133669814927</v>
+        <v>0.1824319538597197</v>
       </c>
       <c r="T68">
-        <v>3.062664364468652</v>
+        <v>3.155472375513157</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0833314869828381</v>
+        <v>0.08208773344578081</v>
       </c>
       <c r="W68">
-        <v>0.2161504353694468</v>
+        <v>0.2164437124534849</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4045217814700878</v>
+        <v>0.3984841429406836</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7153,22 +7153,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2052198321175424</v>
+        <v>0.2071198321175424</v>
       </c>
       <c r="C69">
-        <v>-46.93803971512556</v>
+        <v>-49.50055721829756</v>
       </c>
       <c r="D69">
-        <v>72.85896028487446</v>
+        <v>72.13744278170245</v>
       </c>
       <c r="E69">
-        <v>98.24700000000001</v>
+        <v>100.088</v>
       </c>
       <c r="F69">
-        <v>123.347</v>
+        <v>125.188</v>
       </c>
       <c r="G69">
         <v>3.55</v>
@@ -7189,37 +7189,37 @@
         <v>11.59</v>
       </c>
       <c r="M69">
-        <v>29.0852226</v>
+        <v>29.5193304</v>
       </c>
       <c r="N69">
-        <v>-17.4952226</v>
+        <v>-17.9293304</v>
       </c>
       <c r="O69">
-        <v>-3.604015855600001</v>
+        <v>-3.6934420624</v>
       </c>
       <c r="P69">
-        <v>-13.8912067444</v>
+        <v>-14.2358883376</v>
       </c>
       <c r="Q69">
-        <v>-7.781206744400001</v>
+        <v>-8.125888337599999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1824319538597197</v>
+        <v>0.186701702417836</v>
       </c>
       <c r="T69">
-        <v>3.155472375513157</v>
+        <v>3.254080887247943</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08208773344578081</v>
+        <v>0.08088056089510756</v>
       </c>
       <c r="W69">
-        <v>0.2164437124534849</v>
+        <v>0.2167283637409337</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3984841429406836</v>
+        <v>0.3926240820150853</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7235,22 +7235,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2071198321175424</v>
+        <v>0.2090198321175424</v>
       </c>
       <c r="C70">
-        <v>-49.50055721829756</v>
+        <v>-52.04892456852049</v>
       </c>
       <c r="D70">
-        <v>72.13744278170245</v>
+        <v>71.43007543147952</v>
       </c>
       <c r="E70">
-        <v>100.088</v>
+        <v>101.929</v>
       </c>
       <c r="F70">
-        <v>125.188</v>
+        <v>127.029</v>
       </c>
       <c r="G70">
         <v>3.55</v>
@@ -7271,37 +7271,37 @@
         <v>11.59</v>
       </c>
       <c r="M70">
-        <v>29.5193304</v>
+        <v>29.9534382</v>
       </c>
       <c r="N70">
-        <v>-17.9293304</v>
+        <v>-18.3634382</v>
       </c>
       <c r="O70">
-        <v>-3.6934420624</v>
+        <v>-3.782868269200001</v>
       </c>
       <c r="P70">
-        <v>-14.2358883376</v>
+        <v>-14.5805699308</v>
       </c>
       <c r="Q70">
-        <v>-8.125888337599999</v>
+        <v>-8.470569930800004</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.186701702417836</v>
+        <v>0.1912469186248629</v>
       </c>
       <c r="T70">
-        <v>3.254080887247943</v>
+        <v>3.35905123844949</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08088056089510756</v>
+        <v>0.07970837885314948</v>
       </c>
       <c r="W70">
-        <v>0.2167283637409337</v>
+        <v>0.2170047642664273</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3926240820150853</v>
+        <v>0.3869338779279101</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7317,22 +7317,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2090198321175424</v>
+        <v>0.2109198321175424</v>
       </c>
       <c r="C71">
-        <v>-52.04892456852049</v>
+        <v>-54.58355398553293</v>
       </c>
       <c r="D71">
-        <v>71.43007543147952</v>
+        <v>70.73644601446708</v>
       </c>
       <c r="E71">
-        <v>101.929</v>
+        <v>103.77</v>
       </c>
       <c r="F71">
-        <v>127.029</v>
+        <v>128.87</v>
       </c>
       <c r="G71">
         <v>3.55</v>
@@ -7353,37 +7353,37 @@
         <v>11.59</v>
       </c>
       <c r="M71">
-        <v>29.9534382</v>
+        <v>30.387546</v>
       </c>
       <c r="N71">
-        <v>-18.3634382</v>
+        <v>-18.797546</v>
       </c>
       <c r="O71">
-        <v>-3.782868269200001</v>
+        <v>-3.872294476000001</v>
       </c>
       <c r="P71">
-        <v>-14.5805699308</v>
+        <v>-14.925251524</v>
       </c>
       <c r="Q71">
-        <v>-8.470569930800004</v>
+        <v>-8.815251524000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1912469186248629</v>
+        <v>0.1960951492456917</v>
       </c>
       <c r="T71">
-        <v>3.35905123844949</v>
+        <v>3.471019613064473</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07970837885314948</v>
+        <v>0.07856968772667593</v>
       </c>
       <c r="W71">
-        <v>0.2170047642664273</v>
+        <v>0.2172732676340498</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3869338779279101</v>
+        <v>0.3814062511003685</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7399,22 +7399,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2109198321175424</v>
+        <v>0.2128198321175424</v>
       </c>
       <c r="C72">
-        <v>-54.58355398553293</v>
+        <v>-57.10484183144457</v>
       </c>
       <c r="D72">
-        <v>70.73644601446708</v>
+        <v>70.05615816855544</v>
       </c>
       <c r="E72">
-        <v>103.77</v>
+        <v>105.611</v>
       </c>
       <c r="F72">
-        <v>128.87</v>
+        <v>130.711</v>
       </c>
       <c r="G72">
         <v>3.55</v>
@@ -7435,37 +7435,37 @@
         <v>11.59</v>
       </c>
       <c r="M72">
-        <v>30.387546</v>
+        <v>30.8216538</v>
       </c>
       <c r="N72">
-        <v>-18.797546</v>
+        <v>-19.2316538</v>
       </c>
       <c r="O72">
-        <v>-3.872294476000001</v>
+        <v>-3.961720682800001</v>
       </c>
       <c r="P72">
-        <v>-14.925251524</v>
+        <v>-15.2699331172</v>
       </c>
       <c r="Q72">
-        <v>-8.815251524000004</v>
+        <v>-9.159933117200001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1960951492456917</v>
+        <v>0.2012777405989914</v>
       </c>
       <c r="T72">
-        <v>3.471019613064473</v>
+        <v>3.590709944549455</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07856968772667593</v>
+        <v>0.07746307240658189</v>
       </c>
       <c r="W72">
-        <v>0.2172732676340498</v>
+        <v>0.217534207526528</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3814062511003685</v>
+        <v>0.3760343320707858</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7481,22 +7481,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2128198321175424</v>
+        <v>0.2147198321175424</v>
       </c>
       <c r="C73">
-        <v>-57.10484183144455</v>
+        <v>-59.61316936600393</v>
       </c>
       <c r="D73">
-        <v>70.05615816855544</v>
+        <v>69.38883063399606</v>
       </c>
       <c r="E73">
-        <v>105.611</v>
+        <v>107.452</v>
       </c>
       <c r="F73">
-        <v>130.711</v>
+        <v>132.552</v>
       </c>
       <c r="G73">
         <v>3.55</v>
@@ -7517,37 +7517,37 @@
         <v>11.59</v>
       </c>
       <c r="M73">
-        <v>30.8216538</v>
+        <v>31.2557616</v>
       </c>
       <c r="N73">
-        <v>-19.2316538</v>
+        <v>-19.6657616</v>
       </c>
       <c r="O73">
-        <v>-3.9617206828</v>
+        <v>-4.0511468896</v>
       </c>
       <c r="P73">
-        <v>-15.2699331172</v>
+        <v>-15.6146147104</v>
       </c>
       <c r="Q73">
-        <v>-9.159933117199998</v>
+        <v>-9.504614710399999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2012777405989914</v>
+        <v>0.2068305170489554</v>
       </c>
       <c r="T73">
-        <v>3.590709944549454</v>
+        <v>3.71894958542622</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07746307240658191</v>
+        <v>0.07638719640093493</v>
       </c>
       <c r="W73">
-        <v>0.217534207526528</v>
+        <v>0.2177878990886596</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.376034332070786</v>
+        <v>0.3708116330142472</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7563,22 +7563,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2147198321175424</v>
+        <v>0.2166198321175424</v>
       </c>
       <c r="C74">
-        <v>-59.61316936600393</v>
+        <v>-62.10890345910741</v>
       </c>
       <c r="D74">
-        <v>69.38883063399606</v>
+        <v>68.73409654089259</v>
       </c>
       <c r="E74">
-        <v>107.452</v>
+        <v>109.293</v>
       </c>
       <c r="F74">
-        <v>132.552</v>
+        <v>134.393</v>
       </c>
       <c r="G74">
         <v>3.55</v>
@@ -7599,37 +7599,37 @@
         <v>11.59</v>
       </c>
       <c r="M74">
-        <v>31.2557616</v>
+        <v>31.6898694</v>
       </c>
       <c r="N74">
-        <v>-19.6657616</v>
+        <v>-20.0998694</v>
       </c>
       <c r="O74">
-        <v>-4.0511468896</v>
+        <v>-4.140573096400001</v>
       </c>
       <c r="P74">
-        <v>-15.6146147104</v>
+        <v>-15.9592963036</v>
       </c>
       <c r="Q74">
-        <v>-9.504614710399999</v>
+        <v>-9.849296303600003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2068305170489554</v>
+        <v>0.2127946102729907</v>
       </c>
       <c r="T74">
-        <v>3.71894958542622</v>
+        <v>3.856688458960524</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07638719640093493</v>
+        <v>0.07534079645023718</v>
       </c>
       <c r="W74">
-        <v>0.2177878990886596</v>
+        <v>0.2180346401970341</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3708116330142472</v>
+        <v>0.3657320216030931</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7645,22 +7645,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2166198321175424</v>
+        <v>0.2185198321175424</v>
       </c>
       <c r="C75">
-        <v>-62.10890345910741</v>
+        <v>-64.59239726334657</v>
       </c>
       <c r="D75">
-        <v>68.73409654089259</v>
+        <v>68.09160273665341</v>
       </c>
       <c r="E75">
-        <v>109.293</v>
+        <v>111.134</v>
       </c>
       <c r="F75">
-        <v>134.393</v>
+        <v>136.234</v>
       </c>
       <c r="G75">
         <v>3.55</v>
@@ -7681,37 +7681,37 @@
         <v>11.59</v>
       </c>
       <c r="M75">
-        <v>31.6898694</v>
+        <v>32.1239772</v>
       </c>
       <c r="N75">
-        <v>-20.0998694</v>
+        <v>-20.5339772</v>
       </c>
       <c r="O75">
-        <v>-4.140573096400001</v>
+        <v>-4.229999303200001</v>
       </c>
       <c r="P75">
-        <v>-15.9592963036</v>
+        <v>-16.3039778968</v>
       </c>
       <c r="Q75">
-        <v>-9.849296303600003</v>
+        <v>-10.1939778968</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2127946102729907</v>
+        <v>0.219217479898875</v>
       </c>
       <c r="T75">
-        <v>3.856688458960524</v>
+        <v>4.005022630459006</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07534079645023718</v>
+        <v>0.07432267757928804</v>
       </c>
       <c r="W75">
-        <v>0.2180346401970341</v>
+        <v>0.2182747126268039</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3657320216030931</v>
+        <v>0.3607896969868352</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7727,22 +7727,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2185198321175424</v>
+        <v>0.2204198321175424</v>
       </c>
       <c r="C76">
-        <v>-64.59239726334657</v>
+        <v>-67.0639908491855</v>
       </c>
       <c r="D76">
-        <v>68.09160273665341</v>
+        <v>67.46100915081449</v>
       </c>
       <c r="E76">
-        <v>111.134</v>
+        <v>112.975</v>
       </c>
       <c r="F76">
-        <v>136.234</v>
+        <v>138.075</v>
       </c>
       <c r="G76">
         <v>3.55</v>
@@ -7763,37 +7763,37 @@
         <v>11.59</v>
       </c>
       <c r="M76">
-        <v>32.1239772</v>
+        <v>32.558085</v>
       </c>
       <c r="N76">
-        <v>-20.5339772</v>
+        <v>-20.968085</v>
       </c>
       <c r="O76">
-        <v>-4.229999303200001</v>
+        <v>-4.31942551</v>
       </c>
       <c r="P76">
-        <v>-16.3039778968</v>
+        <v>-16.64865949</v>
       </c>
       <c r="Q76">
-        <v>-10.1939778968</v>
+        <v>-10.53865949</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.219217479898875</v>
+        <v>0.22615417909483</v>
       </c>
       <c r="T76">
-        <v>4.005022630459006</v>
+        <v>4.165223535677367</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07432267757928804</v>
+        <v>0.07333170854489754</v>
       </c>
       <c r="W76">
-        <v>0.2182747126268039</v>
+        <v>0.2185083831251132</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3607896969868352</v>
+        <v>0.3559791676936773</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7809,22 +7809,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2204198321175424</v>
+        <v>0.2223198321175424</v>
       </c>
       <c r="C77">
-        <v>-67.0639908491855</v>
+        <v>-69.5240118051674</v>
       </c>
       <c r="D77">
-        <v>67.46100915081449</v>
+        <v>66.8419881948326</v>
       </c>
       <c r="E77">
-        <v>112.975</v>
+        <v>114.816</v>
       </c>
       <c r="F77">
-        <v>138.075</v>
+        <v>139.916</v>
       </c>
       <c r="G77">
         <v>3.55</v>
@@ -7845,37 +7845,37 @@
         <v>11.59</v>
       </c>
       <c r="M77">
-        <v>32.558085</v>
+        <v>32.9921928</v>
       </c>
       <c r="N77">
-        <v>-20.968085</v>
+        <v>-21.4021928</v>
       </c>
       <c r="O77">
-        <v>-4.31942551</v>
+        <v>-4.4088517168</v>
       </c>
       <c r="P77">
-        <v>-16.64865949</v>
+        <v>-16.9933410832</v>
       </c>
       <c r="Q77">
-        <v>-10.53865949</v>
+        <v>-10.8833410832</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.22615417909483</v>
+        <v>0.2336689365571146</v>
       </c>
       <c r="T77">
-        <v>4.165223535677367</v>
+        <v>4.338774516330591</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07333170854489754</v>
+        <v>0.07236681764299098</v>
       </c>
       <c r="W77">
-        <v>0.2185083831251132</v>
+        <v>0.2187359043997827</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3559791676936773</v>
+        <v>0.3512952312766553</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7891,22 +7891,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2223198321175424</v>
+        <v>0.2242198321175424</v>
       </c>
       <c r="C78">
-        <v>-69.5240118051674</v>
+        <v>-71.97277580537701</v>
       </c>
       <c r="D78">
-        <v>66.8419881948326</v>
+        <v>66.234224194623</v>
       </c>
       <c r="E78">
-        <v>114.816</v>
+        <v>116.657</v>
       </c>
       <c r="F78">
-        <v>139.916</v>
+        <v>141.757</v>
       </c>
       <c r="G78">
         <v>3.55</v>
@@ -7927,37 +7927,37 @@
         <v>11.59</v>
       </c>
       <c r="M78">
-        <v>32.9921928</v>
+        <v>33.4263006</v>
       </c>
       <c r="N78">
-        <v>-21.4021928</v>
+        <v>-21.8363006</v>
       </c>
       <c r="O78">
-        <v>-4.4088517168</v>
+        <v>-4.498277923600002</v>
       </c>
       <c r="P78">
-        <v>-16.9933410832</v>
+        <v>-17.3380226764</v>
       </c>
       <c r="Q78">
-        <v>-10.8833410832</v>
+        <v>-11.2280226764</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2336689365571146</v>
+        <v>0.2418371511900326</v>
       </c>
       <c r="T78">
-        <v>4.338774516330591</v>
+        <v>4.527416886605834</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07236681764299098</v>
+        <v>0.07142698884243265</v>
       </c>
       <c r="W78">
-        <v>0.2187359043997827</v>
+        <v>0.2189575160309544</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3512952312766553</v>
+        <v>0.3467329555457895</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7973,22 +7973,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2242198321175424</v>
+        <v>0.2261198321175424</v>
       </c>
       <c r="C79">
-        <v>-71.97277580537701</v>
+        <v>-74.41058714622373</v>
       </c>
       <c r="D79">
-        <v>66.234224194623</v>
+        <v>65.63741285377628</v>
       </c>
       <c r="E79">
-        <v>116.657</v>
+        <v>118.498</v>
       </c>
       <c r="F79">
-        <v>141.757</v>
+        <v>143.598</v>
       </c>
       <c r="G79">
         <v>3.55</v>
@@ -8009,37 +8009,37 @@
         <v>11.59</v>
       </c>
       <c r="M79">
-        <v>33.4263006</v>
+        <v>33.8604084</v>
       </c>
       <c r="N79">
-        <v>-21.8363006</v>
+        <v>-22.2704084</v>
       </c>
       <c r="O79">
-        <v>-4.498277923600002</v>
+        <v>-4.587704130400001</v>
       </c>
       <c r="P79">
-        <v>-17.3380226764</v>
+        <v>-17.6827042696</v>
       </c>
       <c r="Q79">
-        <v>-11.2280226764</v>
+        <v>-11.5727042696</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2418371511900326</v>
+        <v>0.2507479307895796</v>
       </c>
       <c r="T79">
-        <v>4.527416886605834</v>
+        <v>4.733208563269735</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07142698884243265</v>
+        <v>0.07051125821624762</v>
       </c>
       <c r="W79">
-        <v>0.2189575160309544</v>
+        <v>0.2191734453126088</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3467329555457895</v>
+        <v>0.3422876612439204</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8055,22 +8055,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2261198321175424</v>
+        <v>0.2280198321175424</v>
       </c>
       <c r="C80">
-        <v>-74.41058714622373</v>
+        <v>-76.83773925446364</v>
       </c>
       <c r="D80">
-        <v>65.63741285377628</v>
+        <v>65.05126074553635</v>
       </c>
       <c r="E80">
-        <v>118.498</v>
+        <v>120.339</v>
       </c>
       <c r="F80">
-        <v>143.598</v>
+        <v>145.439</v>
       </c>
       <c r="G80">
         <v>3.55</v>
@@ -8091,37 +8091,37 @@
         <v>11.59</v>
       </c>
       <c r="M80">
-        <v>33.8604084</v>
+        <v>34.2945162</v>
       </c>
       <c r="N80">
-        <v>-22.2704084</v>
+        <v>-22.7045162</v>
       </c>
       <c r="O80">
-        <v>-4.587704130400001</v>
+        <v>-4.677130337199999</v>
       </c>
       <c r="P80">
-        <v>-17.6827042696</v>
+        <v>-18.0273858628</v>
       </c>
       <c r="Q80">
-        <v>-11.5727042696</v>
+        <v>-11.9173858628</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2507479307895796</v>
+        <v>0.2605073560652739</v>
       </c>
       <c r="T80">
-        <v>4.733208563269735</v>
+        <v>4.958599447234961</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07051125821624762</v>
+        <v>0.06961871064389007</v>
       </c>
       <c r="W80">
-        <v>0.2191734453126088</v>
+        <v>0.2193839080301707</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3422876612439204</v>
+        <v>0.3379549060383013</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8137,22 +8137,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2280198321175424</v>
+        <v>0.2299198321175424</v>
       </c>
       <c r="C81">
-        <v>-76.83773925446364</v>
+        <v>-79.25451516824195</v>
       </c>
       <c r="D81">
-        <v>65.05126074553635</v>
+        <v>64.47548483175805</v>
       </c>
       <c r="E81">
-        <v>120.339</v>
+        <v>122.18</v>
       </c>
       <c r="F81">
-        <v>145.439</v>
+        <v>147.28</v>
       </c>
       <c r="G81">
         <v>3.55</v>
@@ -8173,37 +8173,37 @@
         <v>11.59</v>
       </c>
       <c r="M81">
-        <v>34.2945162</v>
+        <v>34.728624</v>
       </c>
       <c r="N81">
-        <v>-22.7045162</v>
+        <v>-23.138624</v>
       </c>
       <c r="O81">
-        <v>-4.677130337199999</v>
+        <v>-4.766556544000001</v>
       </c>
       <c r="P81">
-        <v>-18.0273858628</v>
+        <v>-18.372067456</v>
       </c>
       <c r="Q81">
-        <v>-11.9173858628</v>
+        <v>-12.262067456</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2605073560652739</v>
+        <v>0.2712427238685375</v>
       </c>
       <c r="T81">
-        <v>4.958599447234961</v>
+        <v>5.206529419596709</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06961871064389007</v>
+        <v>0.06874847676084143</v>
       </c>
       <c r="W81">
-        <v>0.2193839080301707</v>
+        <v>0.2195891091797936</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3379549060383013</v>
+        <v>0.3337304697128225</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8219,22 +8219,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2299198321175424</v>
+        <v>0.2318198321175424</v>
       </c>
       <c r="C82">
-        <v>-79.25451516824195</v>
+        <v>-81.66118799281303</v>
       </c>
       <c r="D82">
-        <v>64.47548483175805</v>
+        <v>63.90981200718699</v>
       </c>
       <c r="E82">
-        <v>122.18</v>
+        <v>124.021</v>
       </c>
       <c r="F82">
-        <v>147.28</v>
+        <v>149.121</v>
       </c>
       <c r="G82">
         <v>3.55</v>
@@ -8255,37 +8255,37 @@
         <v>11.59</v>
       </c>
       <c r="M82">
-        <v>34.728624</v>
+        <v>35.1627318</v>
       </c>
       <c r="N82">
-        <v>-23.138624</v>
+        <v>-23.5727318</v>
       </c>
       <c r="O82">
-        <v>-4.766556544000001</v>
+        <v>-4.855982750800001</v>
       </c>
       <c r="P82">
-        <v>-18.372067456</v>
+        <v>-18.7167490492</v>
       </c>
       <c r="Q82">
-        <v>-12.262067456</v>
+        <v>-12.6067490492</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2712427238685375</v>
+        <v>0.2831081303879343</v>
       </c>
       <c r="T82">
-        <v>5.206529419596709</v>
+        <v>5.48055728378601</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06874847676084143</v>
+        <v>0.06789973013416437</v>
       </c>
       <c r="W82">
-        <v>0.2195891091797936</v>
+        <v>0.2197892436343641</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3337304697128225</v>
+        <v>0.3296103404571086</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8301,22 +8301,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2318198321175424</v>
+        <v>0.2337198321175424</v>
       </c>
       <c r="C83">
-        <v>-81.66118799281303</v>
+        <v>-84.05802133247984</v>
       </c>
       <c r="D83">
-        <v>63.90981200718699</v>
+        <v>63.35397866752018</v>
       </c>
       <c r="E83">
-        <v>124.021</v>
+        <v>125.862</v>
       </c>
       <c r="F83">
-        <v>149.121</v>
+        <v>150.962</v>
       </c>
       <c r="G83">
         <v>3.55</v>
@@ -8337,37 +8337,37 @@
         <v>11.59</v>
       </c>
       <c r="M83">
-        <v>35.1627318</v>
+        <v>35.5968396</v>
       </c>
       <c r="N83">
-        <v>-23.5727318</v>
+        <v>-24.0068396</v>
       </c>
       <c r="O83">
-        <v>-4.855982750800001</v>
+        <v>-4.945408957600001</v>
       </c>
       <c r="P83">
-        <v>-18.7167490492</v>
+        <v>-19.0614306424</v>
       </c>
       <c r="Q83">
-        <v>-12.6067490492</v>
+        <v>-12.9514306424</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2831081303879343</v>
+        <v>0.2962919154094862</v>
       </c>
       <c r="T83">
-        <v>5.48055728378601</v>
+        <v>5.785032688440788</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06789973013416437</v>
+        <v>0.06707168464472335</v>
       </c>
       <c r="W83">
-        <v>0.2197892436343641</v>
+        <v>0.2199844967607743</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3296103404571086</v>
+        <v>0.3255907021588512</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8383,22 +8383,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2337198321175424</v>
+        <v>0.2356198321175424</v>
       </c>
       <c r="C84">
-        <v>-84.05802133247984</v>
+        <v>-86.44526970018757</v>
       </c>
       <c r="D84">
-        <v>63.35397866752018</v>
+        <v>62.80773029981243</v>
       </c>
       <c r="E84">
-        <v>125.862</v>
+        <v>127.703</v>
       </c>
       <c r="F84">
-        <v>150.962</v>
+        <v>152.803</v>
       </c>
       <c r="G84">
         <v>3.55</v>
@@ -8419,37 +8419,37 @@
         <v>11.59</v>
       </c>
       <c r="M84">
-        <v>35.5968396</v>
+        <v>36.0309474</v>
       </c>
       <c r="N84">
-        <v>-24.0068396</v>
+        <v>-24.4409474</v>
       </c>
       <c r="O84">
-        <v>-4.945408957600001</v>
+        <v>-5.034835164400001</v>
       </c>
       <c r="P84">
-        <v>-19.0614306424</v>
+        <v>-19.4061122356</v>
       </c>
       <c r="Q84">
-        <v>-12.9514306424</v>
+        <v>-13.2961122356</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2962919154094862</v>
+        <v>0.3110267339629854</v>
       </c>
       <c r="T84">
-        <v>5.785032688440788</v>
+        <v>6.125328728937307</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06707168464472335</v>
+        <v>0.06626359205864234</v>
       </c>
       <c r="W84">
-        <v>0.2199844967607743</v>
+        <v>0.2201750449925721</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3255907021588512</v>
+        <v>0.3216679226147686</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8465,22 +8465,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2356198321175424</v>
+        <v>0.2375198321175424</v>
       </c>
       <c r="C85">
-        <v>-86.44526970018757</v>
+        <v>-88.82317890610931</v>
       </c>
       <c r="D85">
-        <v>62.80773029981243</v>
+        <v>62.2708210938907</v>
       </c>
       <c r="E85">
-        <v>127.703</v>
+        <v>129.544</v>
       </c>
       <c r="F85">
-        <v>152.803</v>
+        <v>154.644</v>
       </c>
       <c r="G85">
         <v>3.55</v>
@@ -8501,37 +8501,37 @@
         <v>11.59</v>
       </c>
       <c r="M85">
-        <v>36.0309474</v>
+        <v>36.4650552</v>
       </c>
       <c r="N85">
-        <v>-24.4409474</v>
+        <v>-24.8750552</v>
       </c>
       <c r="O85">
-        <v>-5.034835164400001</v>
+        <v>-5.124261371200001</v>
       </c>
       <c r="P85">
-        <v>-19.4061122356</v>
+        <v>-19.7507938288</v>
       </c>
       <c r="Q85">
-        <v>-13.2961122356</v>
+        <v>-13.6407938288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3110267339629854</v>
+        <v>0.327603404835672</v>
       </c>
       <c r="T85">
-        <v>6.125328728937307</v>
+        <v>6.508161774495888</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06626359205864234</v>
+        <v>0.06547473977222994</v>
       </c>
       <c r="W85">
-        <v>0.2201750449925721</v>
+        <v>0.2203610563617082</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3216679226147686</v>
+        <v>0.3178385425836404</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8547,22 +8547,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2375198321175424</v>
+        <v>0.2394198321175424</v>
       </c>
       <c r="C86">
-        <v>-88.82317890610926</v>
+        <v>-91.1919864264692</v>
       </c>
       <c r="D86">
-        <v>62.27082109389072</v>
+        <v>61.74301357353078</v>
       </c>
       <c r="E86">
-        <v>129.544</v>
+        <v>131.385</v>
       </c>
       <c r="F86">
-        <v>154.644</v>
+        <v>156.485</v>
       </c>
       <c r="G86">
         <v>3.55</v>
@@ -8583,37 +8583,37 @@
         <v>11.59</v>
       </c>
       <c r="M86">
-        <v>36.46505519999999</v>
+        <v>36.899163</v>
       </c>
       <c r="N86">
-        <v>-24.87505519999999</v>
+        <v>-25.309163</v>
       </c>
       <c r="O86">
-        <v>-5.124261371199999</v>
+        <v>-5.213687578000001</v>
       </c>
       <c r="P86">
-        <v>-19.7507938288</v>
+        <v>-20.095475422</v>
       </c>
       <c r="Q86">
-        <v>-13.6407938288</v>
+        <v>-13.985475422</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3276034048356719</v>
+        <v>0.3463902984913833</v>
       </c>
       <c r="T86">
-        <v>6.508161774495885</v>
+        <v>6.942039226128943</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06547473977222995</v>
+        <v>0.06470444871608605</v>
       </c>
       <c r="W86">
-        <v>0.2203610563617082</v>
+        <v>0.2205426909927469</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3178385425836405</v>
+        <v>0.3140992656120682</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8629,22 +8629,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2394198321175424</v>
+        <v>0.2413198321175424</v>
       </c>
       <c r="C87">
-        <v>-91.1919864264692</v>
+        <v>-93.55192175376708</v>
       </c>
       <c r="D87">
-        <v>61.74301357353078</v>
+        <v>61.22407824623292</v>
       </c>
       <c r="E87">
-        <v>131.385</v>
+        <v>133.226</v>
       </c>
       <c r="F87">
-        <v>156.485</v>
+        <v>158.326</v>
       </c>
       <c r="G87">
         <v>3.55</v>
@@ -8665,37 +8665,37 @@
         <v>11.59</v>
       </c>
       <c r="M87">
-        <v>36.899163</v>
+        <v>37.3332708</v>
       </c>
       <c r="N87">
-        <v>-25.309163</v>
+        <v>-25.7432708</v>
       </c>
       <c r="O87">
-        <v>-5.213687578000001</v>
+        <v>-5.303113784800001</v>
       </c>
       <c r="P87">
-        <v>-20.095475422</v>
+        <v>-20.4401570152</v>
       </c>
       <c r="Q87">
-        <v>-13.985475422</v>
+        <v>-14.3301570152</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3463902984913833</v>
+        <v>0.3678610340979107</v>
       </c>
       <c r="T87">
-        <v>6.942039226128943</v>
+        <v>7.43789917085244</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06470444871608605</v>
+        <v>0.06395207140543389</v>
       </c>
       <c r="W87">
-        <v>0.2205426909927469</v>
+        <v>0.2207201015625987</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3140992656120682</v>
+        <v>0.3104469485700674</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8711,22 +8711,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2413198321175424</v>
+        <v>0.2432198321175424</v>
       </c>
       <c r="C88">
-        <v>-93.55192175376708</v>
+        <v>-95.90320672948839</v>
       </c>
       <c r="D88">
-        <v>61.22407824623292</v>
+        <v>60.71379327051161</v>
       </c>
       <c r="E88">
-        <v>133.226</v>
+        <v>135.067</v>
       </c>
       <c r="F88">
-        <v>158.326</v>
+        <v>160.167</v>
       </c>
       <c r="G88">
         <v>3.55</v>
@@ -8747,37 +8747,37 @@
         <v>11.59</v>
       </c>
       <c r="M88">
-        <v>37.3332708</v>
+        <v>37.7673786</v>
       </c>
       <c r="N88">
-        <v>-25.7432708</v>
+        <v>-26.1773786</v>
       </c>
       <c r="O88">
-        <v>-5.303113784800001</v>
+        <v>-5.392539991600001</v>
       </c>
       <c r="P88">
-        <v>-20.4401570152</v>
+        <v>-20.7848386084</v>
       </c>
       <c r="Q88">
-        <v>-14.3301570152</v>
+        <v>-14.6748386084</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3678610340979107</v>
+        <v>0.39263495979775</v>
       </c>
       <c r="T88">
-        <v>7.43789917085244</v>
+        <v>8.010045260918012</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06395207140543389</v>
+        <v>0.06321699012491167</v>
       </c>
       <c r="W88">
-        <v>0.2207201015625987</v>
+        <v>0.2208934337285458</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3104469485700674</v>
+        <v>0.306878592839377</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8793,22 +8793,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2432198321175424</v>
+        <v>0.2451198321175424</v>
       </c>
       <c r="C89">
-        <v>-95.90320672948839</v>
+        <v>-98.24605586031369</v>
       </c>
       <c r="D89">
-        <v>60.71379327051161</v>
+        <v>60.21194413968632</v>
       </c>
       <c r="E89">
-        <v>135.067</v>
+        <v>136.908</v>
       </c>
       <c r="F89">
-        <v>160.167</v>
+        <v>162.008</v>
       </c>
       <c r="G89">
         <v>3.55</v>
@@ -8829,37 +8829,37 @@
         <v>11.59</v>
       </c>
       <c r="M89">
-        <v>37.7673786</v>
+        <v>38.20148640000001</v>
       </c>
       <c r="N89">
-        <v>-26.1773786</v>
+        <v>-26.61148640000001</v>
       </c>
       <c r="O89">
-        <v>-5.392539991600001</v>
+        <v>-5.481966198400002</v>
       </c>
       <c r="P89">
-        <v>-20.7848386084</v>
+        <v>-21.12952020160001</v>
       </c>
       <c r="Q89">
-        <v>-14.6748386084</v>
+        <v>-15.01952020160001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.39263495979775</v>
+        <v>0.4215378731142292</v>
       </c>
       <c r="T89">
-        <v>8.010045260918012</v>
+        <v>8.677549032661181</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06321699012491167</v>
+        <v>0.06249861523712857</v>
       </c>
       <c r="W89">
-        <v>0.2208934337285458</v>
+        <v>0.2210628265270851</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.306878592839377</v>
+        <v>0.3033913361025659</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8875,22 +8875,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2451198321175424</v>
+        <v>0.2470198321175424</v>
       </c>
       <c r="C90">
-        <v>-98.24605586031369</v>
+        <v>-100.5806766187743</v>
       </c>
       <c r="D90">
-        <v>60.21194413968632</v>
+        <v>59.71832338122569</v>
       </c>
       <c r="E90">
-        <v>136.908</v>
+        <v>138.749</v>
       </c>
       <c r="F90">
-        <v>162.008</v>
+        <v>163.849</v>
       </c>
       <c r="G90">
         <v>3.55</v>
@@ -8911,37 +8911,37 @@
         <v>11.59</v>
       </c>
       <c r="M90">
-        <v>38.20148640000001</v>
+        <v>38.6355942</v>
       </c>
       <c r="N90">
-        <v>-26.61148640000001</v>
+        <v>-27.0455942</v>
       </c>
       <c r="O90">
-        <v>-5.481966198400002</v>
+        <v>-5.5713924052</v>
       </c>
       <c r="P90">
-        <v>-21.12952020160001</v>
+        <v>-21.4742017948</v>
       </c>
       <c r="Q90">
-        <v>-15.01952020160001</v>
+        <v>-15.3642017948</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4215378731142292</v>
+        <v>0.455695861579159</v>
       </c>
       <c r="T90">
-        <v>8.677549032661181</v>
+        <v>9.466417126539469</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06249861523712857</v>
+        <v>0.06179638360525073</v>
       </c>
       <c r="W90">
-        <v>0.2210628265270851</v>
+        <v>0.2212284127458819</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3033913361025659</v>
+        <v>0.2999824446856831</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8957,22 +8957,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2470198321175424</v>
+        <v>0.2489198321175424</v>
       </c>
       <c r="C91">
-        <v>-100.5806766187743</v>
+        <v>-102.9072697292395</v>
       </c>
       <c r="D91">
-        <v>59.71832338122569</v>
+        <v>59.23273027076051</v>
       </c>
       <c r="E91">
-        <v>138.749</v>
+        <v>140.59</v>
       </c>
       <c r="F91">
-        <v>163.849</v>
+        <v>165.69</v>
       </c>
       <c r="G91">
         <v>3.55</v>
@@ -8993,37 +8993,37 @@
         <v>11.59</v>
       </c>
       <c r="M91">
-        <v>38.6355942</v>
+        <v>39.069702</v>
       </c>
       <c r="N91">
-        <v>-27.0455942</v>
+        <v>-27.479702</v>
       </c>
       <c r="O91">
-        <v>-5.5713924052</v>
+        <v>-5.660818612000001</v>
       </c>
       <c r="P91">
-        <v>-21.4742017948</v>
+        <v>-21.818883388</v>
       </c>
       <c r="Q91">
-        <v>-15.3642017948</v>
+        <v>-15.708883388</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.455695861579159</v>
+        <v>0.4966854477370751</v>
       </c>
       <c r="T91">
-        <v>9.466417126539469</v>
+        <v>10.41305883919342</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06179638360525073</v>
+        <v>0.06110975712074794</v>
       </c>
       <c r="W91">
-        <v>0.2212284127458819</v>
+        <v>0.2213903192709276</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2999824446856831</v>
+        <v>0.2966493064113978</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9039,22 +9039,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2489198321175424</v>
+        <v>0.2508198321175424</v>
       </c>
       <c r="C92">
-        <v>-102.9072697292395</v>
+        <v>-105.2260294400632</v>
       </c>
       <c r="D92">
-        <v>59.23273027076051</v>
+        <v>58.7549705599368</v>
       </c>
       <c r="E92">
-        <v>140.59</v>
+        <v>142.431</v>
       </c>
       <c r="F92">
-        <v>165.69</v>
+        <v>167.531</v>
       </c>
       <c r="G92">
         <v>3.55</v>
@@ -9075,37 +9075,37 @@
         <v>11.59</v>
       </c>
       <c r="M92">
-        <v>39.069702</v>
+        <v>39.50380980000001</v>
       </c>
       <c r="N92">
-        <v>-27.479702</v>
+        <v>-27.91380980000001</v>
       </c>
       <c r="O92">
-        <v>-5.660818612000001</v>
+        <v>-5.750244818800001</v>
       </c>
       <c r="P92">
-        <v>-21.818883388</v>
+        <v>-22.1635649812</v>
       </c>
       <c r="Q92">
-        <v>-15.708883388</v>
+        <v>-16.0535649812</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4966854477370751</v>
+        <v>0.5467838308189723</v>
       </c>
       <c r="T92">
-        <v>10.41305883919342</v>
+        <v>11.57006537688158</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06110975712074794</v>
+        <v>0.06043822132821224</v>
       </c>
       <c r="W92">
-        <v>0.2213903192709276</v>
+        <v>0.2215486674108076</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2966493064113978</v>
+        <v>0.2933894239233604</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9121,22 +9121,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2508198321175424</v>
+        <v>0.2527198321175424</v>
       </c>
       <c r="C93">
-        <v>-105.2260294400632</v>
+        <v>-107.5371437826658</v>
       </c>
       <c r="D93">
-        <v>58.7549705599368</v>
+        <v>58.28485621733422</v>
       </c>
       <c r="E93">
-        <v>142.431</v>
+        <v>144.272</v>
       </c>
       <c r="F93">
-        <v>167.531</v>
+        <v>169.372</v>
       </c>
       <c r="G93">
         <v>3.55</v>
@@ -9157,37 +9157,37 @@
         <v>11.59</v>
       </c>
       <c r="M93">
-        <v>39.50380980000001</v>
+        <v>39.93791760000001</v>
       </c>
       <c r="N93">
-        <v>-27.91380980000001</v>
+        <v>-28.34791760000001</v>
       </c>
       <c r="O93">
-        <v>-5.750244818800001</v>
+        <v>-5.839671025600001</v>
       </c>
       <c r="P93">
-        <v>-22.1635649812</v>
+        <v>-22.5082465744</v>
       </c>
       <c r="Q93">
-        <v>-16.0535649812</v>
+        <v>-16.39824657440001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5467838308189723</v>
+        <v>0.6094068096713441</v>
       </c>
       <c r="T93">
-        <v>11.57006537688158</v>
+        <v>13.01632354899178</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06043822132821224</v>
+        <v>0.05978128413986211</v>
       </c>
       <c r="W93">
-        <v>0.2215486674108076</v>
+        <v>0.2217035731998205</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2933894239233604</v>
+        <v>0.2902004084459325</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9203,22 +9203,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2527198321175424</v>
+        <v>0.2546198321175424</v>
       </c>
       <c r="C94">
-        <v>-107.5371437826658</v>
+        <v>-109.8407948182766</v>
       </c>
       <c r="D94">
-        <v>58.28485621733422</v>
+        <v>57.8222051817234</v>
       </c>
       <c r="E94">
-        <v>144.272</v>
+        <v>146.113</v>
       </c>
       <c r="F94">
-        <v>169.372</v>
+        <v>171.213</v>
       </c>
       <c r="G94">
         <v>3.55</v>
@@ -9239,37 +9239,37 @@
         <v>11.59</v>
       </c>
       <c r="M94">
-        <v>39.93791760000001</v>
+        <v>40.3720254</v>
       </c>
       <c r="N94">
-        <v>-28.34791760000001</v>
+        <v>-28.7820254</v>
       </c>
       <c r="O94">
-        <v>-5.839671025600001</v>
+        <v>-5.9290972324</v>
       </c>
       <c r="P94">
-        <v>-22.5082465744</v>
+        <v>-22.8529281676</v>
       </c>
       <c r="Q94">
-        <v>-16.39824657440001</v>
+        <v>-16.7429281676</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6094068096713441</v>
+        <v>0.6899220681958218</v>
       </c>
       <c r="T94">
-        <v>13.01632354899178</v>
+        <v>14.87579834170489</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05978128413986211</v>
+        <v>0.05913847463298188</v>
       </c>
       <c r="W94">
-        <v>0.2217035731998205</v>
+        <v>0.2218551476815429</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2902004084459325</v>
+        <v>0.287079973946514</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9285,22 +9285,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2546198321175424</v>
+        <v>0.2565198321175424</v>
       </c>
       <c r="C95">
-        <v>-109.8407948182766</v>
+        <v>-112.1371588730175</v>
       </c>
       <c r="D95">
-        <v>57.8222051817234</v>
+        <v>57.36684112698246</v>
       </c>
       <c r="E95">
-        <v>146.113</v>
+        <v>147.954</v>
       </c>
       <c r="F95">
-        <v>171.213</v>
+        <v>173.054</v>
       </c>
       <c r="G95">
         <v>3.55</v>
@@ -9321,37 +9321,37 @@
         <v>11.59</v>
       </c>
       <c r="M95">
-        <v>40.3720254</v>
+        <v>40.8061332</v>
       </c>
       <c r="N95">
-        <v>-28.7820254</v>
+        <v>-29.21613320000001</v>
       </c>
       <c r="O95">
-        <v>-5.9290972324</v>
+        <v>-6.018523439200002</v>
       </c>
       <c r="P95">
-        <v>-22.8529281676</v>
+        <v>-23.1976097608</v>
       </c>
       <c r="Q95">
-        <v>-16.7429281676</v>
+        <v>-17.0876097608</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6899220681958218</v>
+        <v>0.797275746228459</v>
       </c>
       <c r="T95">
-        <v>14.87579834170489</v>
+        <v>17.35509806532238</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05913847463298188</v>
+        <v>0.05850934192412036</v>
       </c>
       <c r="W95">
-        <v>0.2218551476815429</v>
+        <v>0.2220034971742924</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.287079973946514</v>
+        <v>0.2840259316704872</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9367,22 +9367,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2565198321175424</v>
+        <v>0.2584198321175424</v>
       </c>
       <c r="C96">
-        <v>-112.1371588730175</v>
+        <v>-114.4264067619655</v>
       </c>
       <c r="D96">
-        <v>57.36684112698246</v>
+        <v>56.91859323803449</v>
       </c>
       <c r="E96">
-        <v>147.954</v>
+        <v>149.795</v>
       </c>
       <c r="F96">
-        <v>173.054</v>
+        <v>174.895</v>
       </c>
       <c r="G96">
         <v>3.55</v>
@@ -9403,37 +9403,37 @@
         <v>11.59</v>
       </c>
       <c r="M96">
-        <v>40.8061332</v>
+        <v>41.240241</v>
       </c>
       <c r="N96">
-        <v>-29.21613320000001</v>
+        <v>-29.650241</v>
       </c>
       <c r="O96">
-        <v>-6.018523439200002</v>
+        <v>-6.107949646000002</v>
       </c>
       <c r="P96">
-        <v>-23.1976097608</v>
+        <v>-23.542291354</v>
       </c>
       <c r="Q96">
-        <v>-17.0876097608</v>
+        <v>-17.432291354</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.797275746228459</v>
+        <v>0.9475708954741512</v>
       </c>
       <c r="T96">
-        <v>17.35509806532238</v>
+        <v>20.82611767838686</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05850934192412036</v>
+        <v>0.05789345411439278</v>
       </c>
       <c r="W96">
-        <v>0.2220034971742924</v>
+        <v>0.2221487235198262</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2840259316704872</v>
+        <v>0.2810361850213242</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9449,22 +9449,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2584198321175424</v>
+        <v>0.2603198321175424</v>
       </c>
       <c r="C97">
-        <v>-114.4264067619655</v>
+        <v>-116.7087040027915</v>
       </c>
       <c r="D97">
-        <v>56.91859323803449</v>
+        <v>56.47729599720854</v>
       </c>
       <c r="E97">
-        <v>149.795</v>
+        <v>151.636</v>
       </c>
       <c r="F97">
-        <v>174.895</v>
+        <v>176.736</v>
       </c>
       <c r="G97">
         <v>3.55</v>
@@ -9485,37 +9485,37 @@
         <v>11.59</v>
       </c>
       <c r="M97">
-        <v>41.240241</v>
+        <v>41.6743488</v>
       </c>
       <c r="N97">
-        <v>-29.650241</v>
+        <v>-30.0843488</v>
       </c>
       <c r="O97">
-        <v>-6.107949646000002</v>
+        <v>-6.197375852800001</v>
       </c>
       <c r="P97">
-        <v>-23.542291354</v>
+        <v>-23.8869729472</v>
       </c>
       <c r="Q97">
-        <v>-17.432291354</v>
+        <v>-17.7769729472</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9475708954741512</v>
+        <v>1.17301361934269</v>
       </c>
       <c r="T97">
-        <v>20.82611767838686</v>
+        <v>26.03264709798359</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05789345411439278</v>
+        <v>0.05729039730070119</v>
       </c>
       <c r="W97">
-        <v>0.2221487235198262</v>
+        <v>0.2222909243164947</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2810361850213242</v>
+        <v>0.2781087247606854</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9531,22 +9531,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2603198321175424</v>
+        <v>0.2622198321175424</v>
       </c>
       <c r="C98">
-        <v>-116.7087040027914</v>
+        <v>-118.984211019538</v>
       </c>
       <c r="D98">
-        <v>56.47729599720854</v>
+        <v>56.04278898046201</v>
       </c>
       <c r="E98">
-        <v>151.636</v>
+        <v>153.477</v>
       </c>
       <c r="F98">
-        <v>176.736</v>
+        <v>178.577</v>
       </c>
       <c r="G98">
         <v>3.55</v>
@@ -9567,37 +9567,37 @@
         <v>11.59</v>
       </c>
       <c r="M98">
-        <v>41.6743488</v>
+        <v>42.1084566</v>
       </c>
       <c r="N98">
-        <v>-30.0843488</v>
+        <v>-30.5184566</v>
       </c>
       <c r="O98">
-        <v>-6.1973758528</v>
+        <v>-6.286802059600001</v>
       </c>
       <c r="P98">
-        <v>-23.8869729472</v>
+        <v>-24.2316545404</v>
       </c>
       <c r="Q98">
-        <v>-17.7769729472</v>
+        <v>-18.1216545404</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.173013619342687</v>
+        <v>1.548751492456916</v>
       </c>
       <c r="T98">
-        <v>26.03264709798352</v>
+        <v>34.7101961306447</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05729039730070121</v>
+        <v>0.05669977464811664</v>
       </c>
       <c r="W98">
-        <v>0.2222909243164947</v>
+        <v>0.2224301931379741</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2781087247606854</v>
+        <v>0.2752416245054206</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9613,22 +9613,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2622198321175424</v>
+        <v>0.2641198321175424</v>
       </c>
       <c r="C99">
-        <v>-118.984211019538</v>
+        <v>-121.2530833370621</v>
       </c>
       <c r="D99">
-        <v>56.04278898046201</v>
+        <v>55.6149166629379</v>
       </c>
       <c r="E99">
-        <v>153.477</v>
+        <v>155.318</v>
       </c>
       <c r="F99">
-        <v>178.577</v>
+        <v>180.418</v>
       </c>
       <c r="G99">
         <v>3.55</v>
@@ -9649,37 +9649,37 @@
         <v>11.59</v>
       </c>
       <c r="M99">
-        <v>42.1084566</v>
+        <v>42.5425644</v>
       </c>
       <c r="N99">
-        <v>-30.5184566</v>
+        <v>-30.9525644</v>
       </c>
       <c r="O99">
-        <v>-6.286802059600001</v>
+        <v>-6.3762282664</v>
       </c>
       <c r="P99">
-        <v>-24.2316545404</v>
+        <v>-24.57633613359999</v>
       </c>
       <c r="Q99">
-        <v>-18.1216545404</v>
+        <v>-18.4663361336</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.548751492456916</v>
+        <v>2.300227238685373</v>
       </c>
       <c r="T99">
-        <v>34.7101961306447</v>
+        <v>52.06529419596704</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05669977464811664</v>
+        <v>0.05612120551905424</v>
       </c>
       <c r="W99">
-        <v>0.2224301931379741</v>
+        <v>0.222566619738607</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2752416245054206</v>
+        <v>0.2724330365002633</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9695,22 +9695,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2641198321175424</v>
+        <v>0.2660198321175424</v>
       </c>
       <c r="C100">
-        <v>-121.2530833370621</v>
+        <v>-123.5154717666381</v>
       </c>
       <c r="D100">
-        <v>55.6149166629379</v>
+        <v>55.19352823336184</v>
       </c>
       <c r="E100">
-        <v>155.318</v>
+        <v>157.159</v>
       </c>
       <c r="F100">
-        <v>180.418</v>
+        <v>182.259</v>
       </c>
       <c r="G100">
         <v>3.55</v>
@@ -9731,37 +9731,37 @@
         <v>11.59</v>
       </c>
       <c r="M100">
-        <v>42.5425644</v>
+        <v>42.9766722</v>
       </c>
       <c r="N100">
-        <v>-30.9525644</v>
+        <v>-31.3866722</v>
       </c>
       <c r="O100">
-        <v>-6.3762282664</v>
+        <v>-6.4656544732</v>
       </c>
       <c r="P100">
-        <v>-24.57633613359999</v>
+        <v>-24.9210177268</v>
       </c>
       <c r="Q100">
-        <v>-18.4663361336</v>
+        <v>-18.8110177268</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.300227238685373</v>
+        <v>4.554654477370746</v>
       </c>
       <c r="T100">
-        <v>52.06529419596704</v>
+        <v>104.1305883919341</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05612120551905424</v>
+        <v>0.05555432465522541</v>
       </c>
       <c r="W100">
-        <v>0.222566619738607</v>
+        <v>0.2227002902462979</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9769,91 +9769,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2724330365002633</v>
+        <v>0.2696811876467252</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2660198321175424</v>
-      </c>
-      <c r="C101">
-        <v>-123.5154717666381</v>
-      </c>
-      <c r="D101">
-        <v>55.19352823336184</v>
-      </c>
-      <c r="E101">
-        <v>157.159</v>
-      </c>
-      <c r="F101">
-        <v>182.259</v>
-      </c>
-      <c r="G101">
-        <v>3.55</v>
-      </c>
-      <c r="H101">
-        <v>159</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>17.7</v>
-      </c>
-      <c r="K101">
-        <v>6.11</v>
-      </c>
-      <c r="L101">
-        <v>11.59</v>
-      </c>
-      <c r="M101">
-        <v>42.9766722</v>
-      </c>
-      <c r="N101">
-        <v>-31.3866722</v>
-      </c>
-      <c r="O101">
-        <v>-6.4656544732</v>
-      </c>
-      <c r="P101">
-        <v>-24.9210177268</v>
-      </c>
-      <c r="Q101">
-        <v>-18.8110177268</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.554654477370746</v>
-      </c>
-      <c r="T101">
-        <v>104.1305883919341</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05555432465522541</v>
-      </c>
-      <c r="W101">
-        <v>0.2227002902462979</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2696811876467252</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
